--- a/Sabana Datos/dataset_completo.xlsx
+++ b/Sabana Datos/dataset_completo.xlsx
@@ -535,119 +535,119 @@
   <dimension ref="A1:DI85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="true"/>
-    <col min="2" max="2" width="10.28515625" customWidth="true"/>
-    <col min="3" max="3" width="6.28515625" customWidth="true"/>
-    <col min="4" max="4" width="9.42578125" customWidth="true"/>
-    <col min="5" max="5" width="9.42578125" customWidth="true"/>
-    <col min="6" max="6" width="9.42578125" customWidth="true"/>
-    <col min="7" max="7" width="11.140625" customWidth="true"/>
-    <col min="8" max="8" width="11.140625" customWidth="true"/>
-    <col min="9" max="9" width="11.140625" customWidth="true"/>
-    <col min="10" max="10" width="8" customWidth="true"/>
-    <col min="11" max="11" width="8" customWidth="true"/>
-    <col min="12" max="12" width="8" customWidth="true"/>
-    <col min="13" max="13" width="8" customWidth="true"/>
-    <col min="14" max="14" width="9.7109375" customWidth="true"/>
-    <col min="15" max="15" width="9.7109375" customWidth="true"/>
-    <col min="16" max="16" width="9.7109375" customWidth="true"/>
-    <col min="17" max="17" width="9.7109375" customWidth="true"/>
-    <col min="18" max="18" width="9.28515625" customWidth="true"/>
-    <col min="19" max="19" width="11" customWidth="true"/>
-    <col min="20" max="20" width="11.7109375" customWidth="true"/>
-    <col min="21" max="21" width="13.28515625" customWidth="true"/>
-    <col min="22" max="22" width="12.5703125" customWidth="true"/>
-    <col min="23" max="23" width="10.7109375" customWidth="true"/>
-    <col min="24" max="24" width="12.7109375" customWidth="true"/>
-    <col min="25" max="25" width="12.42578125" customWidth="true"/>
-    <col min="26" max="26" width="20.28515625" customWidth="true"/>
-    <col min="27" max="27" width="21.85546875" customWidth="true"/>
-    <col min="28" max="28" width="21.140625" customWidth="true"/>
-    <col min="29" max="29" width="14" customWidth="true"/>
-    <col min="30" max="30" width="15.5703125" customWidth="true"/>
-    <col min="31" max="31" width="14.85546875" customWidth="true"/>
-    <col min="32" max="32" width="9.7109375" customWidth="true"/>
-    <col min="33" max="33" width="6.7109375" customWidth="true"/>
-    <col min="34" max="34" width="6.7109375" customWidth="true"/>
-    <col min="35" max="35" width="6.7109375" customWidth="true"/>
-    <col min="36" max="36" width="22.85546875" customWidth="true"/>
-    <col min="37" max="37" width="21.85546875" customWidth="true"/>
-    <col min="38" max="38" width="19.28515625" customWidth="true"/>
-    <col min="39" max="39" width="14.28515625" customWidth="true"/>
-    <col min="40" max="40" width="22.5703125" customWidth="true"/>
-    <col min="41" max="41" width="31.85546875" customWidth="true"/>
-    <col min="42" max="42" width="31.28515625" customWidth="true"/>
-    <col min="43" max="43" width="30.140625" customWidth="true"/>
-    <col min="44" max="44" width="20.140625" customWidth="true"/>
-    <col min="45" max="45" width="29.85546875" customWidth="true"/>
-    <col min="46" max="46" width="17.7109375" customWidth="true"/>
-    <col min="47" max="47" width="31.7109375" customWidth="true"/>
-    <col min="48" max="48" width="24.7109375" customWidth="true"/>
-    <col min="49" max="49" width="16.85546875" customWidth="true"/>
-    <col min="50" max="50" width="29.5703125" customWidth="true"/>
-    <col min="51" max="51" width="28.85546875" customWidth="true"/>
-    <col min="52" max="52" width="20.7109375" customWidth="true"/>
-    <col min="53" max="53" width="20.85546875" customWidth="true"/>
-    <col min="54" max="54" width="19" customWidth="true"/>
-    <col min="55" max="55" width="29.85546875" customWidth="true"/>
-    <col min="56" max="56" width="32.140625" customWidth="true"/>
-    <col min="57" max="57" width="29.85546875" customWidth="true"/>
-    <col min="58" max="58" width="30.85546875" customWidth="true"/>
-    <col min="59" max="59" width="26.42578125" customWidth="true"/>
-    <col min="60" max="60" width="25.42578125" customWidth="true"/>
-    <col min="61" max="61" width="20.85546875" customWidth="true"/>
-    <col min="62" max="62" width="35.140625" customWidth="true"/>
-    <col min="63" max="63" width="27.5703125" customWidth="true"/>
-    <col min="64" max="64" width="28.7109375" customWidth="true"/>
-    <col min="65" max="65" width="34.28515625" customWidth="true"/>
-    <col min="66" max="66" width="44.140625" customWidth="true"/>
-    <col min="67" max="67" width="33.28515625" customWidth="true"/>
-    <col min="68" max="68" width="32.42578125" customWidth="true"/>
-    <col min="69" max="69" width="24.85546875" customWidth="true"/>
-    <col min="70" max="70" width="25" customWidth="true"/>
-    <col min="71" max="71" width="26" customWidth="true"/>
-    <col min="72" max="72" width="16.140625" customWidth="true"/>
-    <col min="73" max="73" width="36.140625" customWidth="true"/>
-    <col min="74" max="74" width="27.42578125" customWidth="true"/>
-    <col min="75" max="75" width="27.28515625" customWidth="true"/>
-    <col min="76" max="76" width="28.85546875" customWidth="true"/>
-    <col min="77" max="77" width="29.140625" customWidth="true"/>
-    <col min="78" max="78" width="27.42578125" customWidth="true"/>
-    <col min="79" max="79" width="17.5703125" customWidth="true"/>
-    <col min="80" max="80" width="34" customWidth="true"/>
-    <col min="81" max="81" width="34.28515625" customWidth="true"/>
-    <col min="82" max="82" width="9.42578125" customWidth="true"/>
-    <col min="83" max="83" width="8.5703125" customWidth="true"/>
-    <col min="84" max="84" width="11.85546875" customWidth="true"/>
-    <col min="85" max="85" width="8.140625" customWidth="true"/>
-    <col min="86" max="86" width="10.140625" customWidth="true"/>
-    <col min="87" max="87" width="10.7109375" customWidth="true"/>
-    <col min="88" max="88" width="11.7109375" customWidth="true"/>
-    <col min="89" max="89" width="9" customWidth="true"/>
-    <col min="90" max="90" width="10.7109375" customWidth="true"/>
-    <col min="91" max="91" width="10.140625" customWidth="true"/>
-    <col min="92" max="92" width="10.85546875" customWidth="true"/>
-    <col min="93" max="93" width="10.42578125" customWidth="true"/>
-    <col min="94" max="94" width="11" customWidth="true"/>
-    <col min="95" max="95" width="11.7109375" customWidth="true"/>
-    <col min="96" max="96" width="15.42578125" customWidth="true"/>
-    <col min="97" max="97" width="14.42578125" customWidth="true"/>
-    <col min="98" max="98" width="13.7109375" customWidth="true"/>
-    <col min="99" max="99" width="14.42578125" customWidth="true"/>
-    <col min="100" max="100" width="14.42578125" customWidth="true"/>
-    <col min="101" max="101" width="13.7109375" customWidth="true"/>
-    <col min="102" max="102" width="15.7109375" customWidth="true"/>
-    <col min="103" max="103" width="15.28515625" customWidth="true"/>
-    <col min="104" max="104" width="15.5703125" customWidth="true"/>
-    <col min="105" max="105" width="15.7109375" customWidth="true"/>
-    <col min="106" max="106" width="14.7109375" customWidth="true"/>
-    <col min="107" max="107" width="14.42578125" customWidth="true"/>
-    <col min="108" max="108" width="16.42578125" customWidth="true"/>
-    <col min="109" max="109" width="16.5703125" customWidth="true"/>
-    <col min="110" max="110" width="13.42578125" customWidth="true"/>
-    <col min="111" max="111" width="14.42578125" customWidth="true"/>
-    <col min="112" max="112" width="14.42578125" customWidth="true"/>
-    <col min="113" max="113" width="15.85546875" customWidth="true"/>
+    <col min="1" max="1" width="4.77734375" customWidth="true"/>
+    <col min="2" max="2" width="9.21875" customWidth="true"/>
+    <col min="3" max="3" width="5.6640625" customWidth="true"/>
+    <col min="4" max="4" width="8.5546875" customWidth="true"/>
+    <col min="5" max="5" width="8.5546875" customWidth="true"/>
+    <col min="6" max="6" width="8.5546875" customWidth="true"/>
+    <col min="7" max="7" width="10.21875" customWidth="true"/>
+    <col min="8" max="8" width="10.21875" customWidth="true"/>
+    <col min="9" max="9" width="10.21875" customWidth="true"/>
+    <col min="10" max="10" width="7.33203125" customWidth="true"/>
+    <col min="11" max="11" width="7.33203125" customWidth="true"/>
+    <col min="12" max="12" width="7.33203125" customWidth="true"/>
+    <col min="13" max="13" width="7.33203125" customWidth="true"/>
+    <col min="14" max="14" width="9" customWidth="true"/>
+    <col min="15" max="15" width="9" customWidth="true"/>
+    <col min="16" max="16" width="9" customWidth="true"/>
+    <col min="17" max="17" width="9" customWidth="true"/>
+    <col min="18" max="18" width="8.44140625" customWidth="true"/>
+    <col min="19" max="19" width="10.109375" customWidth="true"/>
+    <col min="20" max="20" width="10.77734375" customWidth="true"/>
+    <col min="21" max="21" width="12.33203125" customWidth="true"/>
+    <col min="22" max="22" width="11.77734375" customWidth="true"/>
+    <col min="23" max="23" width="10" customWidth="true"/>
+    <col min="24" max="24" width="12" customWidth="true"/>
+    <col min="25" max="25" width="11.6640625" customWidth="true"/>
+    <col min="26" max="26" width="18.77734375" customWidth="true"/>
+    <col min="27" max="27" width="20.33203125" customWidth="true"/>
+    <col min="28" max="28" width="19.77734375" customWidth="true"/>
+    <col min="29" max="29" width="13" customWidth="true"/>
+    <col min="30" max="30" width="14.5546875" customWidth="true"/>
+    <col min="31" max="31" width="14" customWidth="true"/>
+    <col min="32" max="32" width="8.88671875" customWidth="true"/>
+    <col min="33" max="33" width="6.33203125" customWidth="true"/>
+    <col min="34" max="34" width="6.33203125" customWidth="true"/>
+    <col min="35" max="35" width="6.33203125" customWidth="true"/>
+    <col min="36" max="36" width="21" customWidth="true"/>
+    <col min="37" max="37" width="20.21875" customWidth="true"/>
+    <col min="38" max="38" width="17.88671875" customWidth="true"/>
+    <col min="39" max="39" width="13.44140625" customWidth="true"/>
+    <col min="40" max="40" width="21" customWidth="true"/>
+    <col min="41" max="41" width="29.44140625" customWidth="true"/>
+    <col min="42" max="42" width="29" customWidth="true"/>
+    <col min="43" max="43" width="27.6640625" customWidth="true"/>
+    <col min="44" max="44" width="18.6640625" customWidth="true"/>
+    <col min="45" max="45" width="27.6640625" customWidth="true"/>
+    <col min="46" max="46" width="16.44140625" customWidth="true"/>
+    <col min="47" max="47" width="29" customWidth="true"/>
+    <col min="48" max="48" width="23.109375" customWidth="true"/>
+    <col min="49" max="49" width="15.88671875" customWidth="true"/>
+    <col min="50" max="50" width="27.77734375" customWidth="true"/>
+    <col min="51" max="51" width="26.77734375" customWidth="true"/>
+    <col min="52" max="52" width="19.109375" customWidth="true"/>
+    <col min="53" max="53" width="19.33203125" customWidth="true"/>
+    <col min="54" max="54" width="17.44140625" customWidth="true"/>
+    <col min="55" max="55" width="27.6640625" customWidth="true"/>
+    <col min="56" max="56" width="29.6640625" customWidth="true"/>
+    <col min="57" max="57" width="27.44140625" customWidth="true"/>
+    <col min="58" max="58" width="28.77734375" customWidth="true"/>
+    <col min="59" max="59" width="24.33203125" customWidth="true"/>
+    <col min="60" max="60" width="23.77734375" customWidth="true"/>
+    <col min="61" max="61" width="19.44140625" customWidth="true"/>
+    <col min="62" max="62" width="32" customWidth="true"/>
+    <col min="63" max="63" width="25.5546875" customWidth="true"/>
+    <col min="64" max="64" width="26.44140625" customWidth="true"/>
+    <col min="65" max="65" width="31.33203125" customWidth="true"/>
+    <col min="66" max="66" width="41" customWidth="true"/>
+    <col min="67" max="67" width="30.6640625" customWidth="true"/>
+    <col min="68" max="68" width="29.77734375" customWidth="true"/>
+    <col min="69" max="69" width="22.88671875" customWidth="true"/>
+    <col min="70" max="70" width="23.44140625" customWidth="true"/>
+    <col min="71" max="71" width="24.33203125" customWidth="true"/>
+    <col min="72" max="72" width="15.33203125" customWidth="true"/>
+    <col min="73" max="73" width="33.21875" customWidth="true"/>
+    <col min="74" max="74" width="25.5546875" customWidth="true"/>
+    <col min="75" max="75" width="25.44140625" customWidth="true"/>
+    <col min="76" max="76" width="26.77734375" customWidth="true"/>
+    <col min="77" max="77" width="27.109375" customWidth="true"/>
+    <col min="78" max="78" width="25.5546875" customWidth="true"/>
+    <col min="79" max="79" width="16.44140625" customWidth="true"/>
+    <col min="80" max="80" width="31.5546875" customWidth="true"/>
+    <col min="81" max="81" width="31.6640625" customWidth="true"/>
+    <col min="82" max="82" width="8.88671875" customWidth="true"/>
+    <col min="83" max="83" width="8.109375" customWidth="true"/>
+    <col min="84" max="84" width="11.33203125" customWidth="true"/>
+    <col min="85" max="85" width="7.77734375" customWidth="true"/>
+    <col min="86" max="86" width="9.5546875" customWidth="true"/>
+    <col min="87" max="87" width="10" customWidth="true"/>
+    <col min="88" max="88" width="11.5546875" customWidth="true"/>
+    <col min="89" max="89" width="8.33203125" customWidth="true"/>
+    <col min="90" max="90" width="10.33203125" customWidth="true"/>
+    <col min="91" max="91" width="9.33203125" customWidth="true"/>
+    <col min="92" max="92" width="10.21875" customWidth="true"/>
+    <col min="93" max="93" width="10" customWidth="true"/>
+    <col min="94" max="94" width="10.33203125" customWidth="true"/>
+    <col min="95" max="95" width="10.88671875" customWidth="true"/>
+    <col min="96" max="96" width="15.21875" customWidth="true"/>
+    <col min="97" max="97" width="14.21875" customWidth="true"/>
+    <col min="98" max="98" width="13.5546875" customWidth="true"/>
+    <col min="99" max="99" width="14.21875" customWidth="true"/>
+    <col min="100" max="100" width="14.21875" customWidth="true"/>
+    <col min="101" max="101" width="13.5546875" customWidth="true"/>
+    <col min="102" max="102" width="15.5546875" customWidth="true"/>
+    <col min="103" max="103" width="14.21875" customWidth="true"/>
+    <col min="104" max="104" width="15.21875" customWidth="true"/>
+    <col min="105" max="105" width="15.5546875" customWidth="true"/>
+    <col min="106" max="106" width="13.6640625" customWidth="true"/>
+    <col min="107" max="107" width="15.21875" customWidth="true"/>
+    <col min="108" max="108" width="15.5546875" customWidth="true"/>
+    <col min="109" max="109" width="14.21875" customWidth="true"/>
+    <col min="110" max="110" width="15.21875" customWidth="true"/>
+    <col min="111" max="111" width="14.21875" customWidth="true"/>
+    <col min="112" max="112" width="14.5546875" customWidth="true"/>
+    <col min="113" max="113" width="14.21875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,40 +1296,40 @@
         <v>0.92704612474911996</v>
       </c>
       <c r="CX2" s="0">
-        <v>1.48505528664597e-08</v>
+        <v>1.4924234696747601e-08</v>
       </c>
       <c r="CY2" s="0">
-        <v>0.255226181372608</v>
+        <v>0.72679724470339901</v>
       </c>
       <c r="CZ2" s="0">
-        <v>1.8195209122154099</v>
+        <v>1.8195218945812499</v>
       </c>
       <c r="DA2" s="0">
-        <v>-0.22398290135840301</v>
+        <v>1.7585353415989299e-09</v>
       </c>
       <c r="DB2" s="0">
-        <v>-0.60863352569138096</v>
+        <v>0.68108742212788898</v>
       </c>
       <c r="DC2" s="0">
-        <v>1.5642320639112901</v>
+        <v>1.8195215683008901</v>
       </c>
       <c r="DD2" s="0">
-        <v>0.000428883872673744</v>
+        <v>0.00043261228452632901</v>
       </c>
       <c r="DE2" s="0">
-        <v>-1.6563937111245699</v>
+        <v>0.70996095901203005</v>
       </c>
       <c r="DF2" s="0">
-        <v>1.82120830548208</v>
+        <v>1.8212503392181301</v>
       </c>
       <c r="DG2" s="0">
-        <v>-0.25522616652205515</v>
+        <v>-0.72679722977916428</v>
       </c>
       <c r="DH2" s="0">
-        <v>0.38465062433297792</v>
+        <v>-0.68108742036935366</v>
       </c>
       <c r="DI2" s="0">
-        <v>1.6568225949972437</v>
+        <v>-0.70952834672750376</v>
       </c>
     </row>
     <row r="3">
@@ -1637,40 +1637,40 @@
         <v>0.60494127305488998</v>
       </c>
       <c r="CX3" s="0">
-        <v>1.6205557685464799e-07</v>
+        <v>1.5152813341831901e-07</v>
       </c>
       <c r="CY3" s="0">
-        <v>0.25121017929086498</v>
+        <v>0.71706542918278604</v>
       </c>
       <c r="CZ3" s="0">
-        <v>1.51360680906905</v>
+        <v>1.5136059283347301</v>
       </c>
       <c r="DA3" s="0">
-        <v>-0.0265307059383793</v>
+        <v>6.3861588319930598e-08</v>
       </c>
       <c r="DB3" s="0">
-        <v>-0.90330449812448299</v>
+        <v>0.73177620812885902</v>
       </c>
       <c r="DC3" s="0">
-        <v>1.48253691070549</v>
+        <v>1.51360569502095</v>
       </c>
       <c r="DD3" s="0">
-        <v>0.0158069019430499</v>
+        <v>0.015805371668726399</v>
       </c>
       <c r="DE3" s="0">
-        <v>-0.97193667184376797</v>
+        <v>0.69011335083041003</v>
       </c>
       <c r="DF3" s="0">
-        <v>1.55879688413024</v>
+        <v>1.5588273867053599</v>
       </c>
       <c r="DG3" s="0">
-        <v>-0.25121001723528813</v>
+        <v>-0.71706527765465267</v>
       </c>
       <c r="DH3" s="0">
-        <v>0.87677379218610374</v>
+        <v>-0.73177614426727067</v>
       </c>
       <c r="DI3" s="0">
-        <v>0.98774357378681787</v>
+        <v>-0.67430797916168361</v>
       </c>
     </row>
     <row r="4">
@@ -1978,40 +1978,40 @@
         <v>0.86365966243454195</v>
       </c>
       <c r="CX4" s="0">
-        <v>2.6580093912461199e-09</v>
+        <v>1.4393815425029799e-08</v>
       </c>
       <c r="CY4" s="0">
-        <v>0.25005232893581197</v>
+        <v>0.75005326865598798</v>
       </c>
       <c r="CZ4" s="0">
-        <v>20.402800524072799</v>
+        <v>18.837836752021602</v>
       </c>
       <c r="DA4" s="0">
-        <v>-24.965</v>
+        <v>4.53176926514867e-08</v>
       </c>
       <c r="DB4" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.72452799175771798</v>
       </c>
       <c r="DC4" s="0">
-        <v>37.108333333333299</v>
+        <v>18.5805086084296</v>
       </c>
       <c r="DD4" s="0">
-        <v>-0.24455113207891399</v>
+        <v>4.4701824257886297e-08</v>
       </c>
       <c r="DE4" s="0">
-        <v>-214.12906752292</v>
+        <v>0.75000003996341602</v>
       </c>
       <c r="DF4" s="0">
-        <v>121.357744015259</v>
+        <v>18.837092869611102</v>
       </c>
       <c r="DG4" s="0">
-        <v>-0.25005232627780261</v>
+        <v>-0.75005325426217251</v>
       </c>
       <c r="DH4" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.72452794644002538</v>
       </c>
       <c r="DI4" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.74999999526159178</v>
       </c>
     </row>
     <row r="5">
@@ -2319,40 +2319,40 @@
         <v>0.83003896536148603</v>
       </c>
       <c r="CX5" s="0">
-        <v>1.76662183126797e-10</v>
+        <v>5.4146245636362297e-11</v>
       </c>
       <c r="CY5" s="0">
-        <v>0.39710585122168901</v>
+        <v>0.54218260242185601</v>
       </c>
       <c r="CZ5" s="0">
-        <v>15.0618464242551</v>
+        <v>49.852019880382798</v>
       </c>
       <c r="DA5" s="0">
-        <v>-24.965</v>
+        <v>4.2782436009718498e-08</v>
       </c>
       <c r="DB5" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000037404808595</v>
       </c>
       <c r="DC5" s="0">
-        <v>37.108333333333299</v>
+        <v>18.699227172577501</v>
       </c>
       <c r="DD5" s="0">
-        <v>-0.123978190677758</v>
+        <v>9.7224264282238395e-07</v>
       </c>
       <c r="DE5" s="0">
-        <v>-583.46484614639701</v>
+        <v>0.82898490473446595</v>
       </c>
       <c r="DF5" s="0">
-        <v>329.50364539382798</v>
+        <v>22.053387600867499</v>
       </c>
       <c r="DG5" s="0">
-        <v>-0.39710585104502683</v>
+        <v>-0.54218260236770977</v>
       </c>
       <c r="DH5" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75000033126564991</v>
       </c>
       <c r="DI5" s="0">
-        <v>583.3408679557192</v>
+        <v>-0.82898393249182312</v>
       </c>
     </row>
     <row r="6">
@@ -2660,40 +2660,40 @@
         <v>0.83533951395125905</v>
       </c>
       <c r="CX6" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY6" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ6" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA6" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB6" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC6" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD6" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE6" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF6" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG6" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH6" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI6" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="7">
@@ -3001,40 +3001,40 @@
         <v>0.80576443660417996</v>
       </c>
       <c r="CX7" s="0">
-        <v>0.113428840416073</v>
+        <v>0.11342883987746</v>
       </c>
       <c r="CY7" s="0">
-        <v>0.25031443117236202</v>
+        <v>0.79494555600145</v>
       </c>
       <c r="CZ7" s="0">
-        <v>1.84772540430773</v>
+        <v>1.8477254363569899</v>
       </c>
       <c r="DA7" s="0">
-        <v>0.32225219439250502</v>
+        <v>0.32224342361686598</v>
       </c>
       <c r="DB7" s="0">
-        <v>-0.52178531009246498</v>
+        <v>0.74888683224942398</v>
       </c>
       <c r="DC7" s="0">
-        <v>1.5511855577145599</v>
+        <v>1.5511551737552101</v>
       </c>
       <c r="DD7" s="0">
-        <v>0.22670059173009799</v>
+        <v>0.226708185832589</v>
       </c>
       <c r="DE7" s="0">
-        <v>-0.68452563240022102</v>
+        <v>0.78845431372007901</v>
       </c>
       <c r="DF7" s="0">
-        <v>1.75570299001483</v>
+        <v>1.7556762722160799</v>
       </c>
       <c r="DG7" s="0">
-        <v>-0.13688559075628903</v>
+        <v>-0.68151671612399001</v>
       </c>
       <c r="DH7" s="0">
-        <v>0.84403750448496995</v>
+        <v>-0.42664340863255801</v>
       </c>
       <c r="DI7" s="0">
-        <v>0.91122622413031906</v>
+        <v>-0.56174612788749001</v>
       </c>
     </row>
     <row r="8">
@@ -3332,40 +3332,40 @@
         <v>0.58244266476348805</v>
       </c>
       <c r="CX8" s="0">
-        <v>0.49999983863143499</v>
+        <v>0.60556729637479301</v>
       </c>
       <c r="CY8" s="0">
-        <v>0.25009458576326199</v>
+        <v>0.659449238074578</v>
       </c>
       <c r="CZ8" s="0">
-        <v>1.02527319361708</v>
+        <v>0.941453441986705</v>
       </c>
       <c r="DA8" s="0">
-        <v>1.51521643470344</v>
+        <v>1.49999545794486</v>
       </c>
       <c r="DB8" s="0">
-        <v>-1.9019715924056899</v>
+        <v>0.75013163685165796</v>
       </c>
       <c r="DC8" s="0">
-        <v>1.32606777499458</v>
+        <v>1.3341916705091099</v>
       </c>
       <c r="DD8" s="0">
-        <v>4472583249713.6699</v>
+        <v>1.4999994899506399</v>
       </c>
       <c r="DE8" s="0">
-        <v>-4961489673391.5596</v>
+        <v>0.88568205542998901</v>
       </c>
       <c r="DF8" s="0">
-        <v>3.3863869843052701</v>
+        <v>4.2978516742179904</v>
       </c>
       <c r="DG8" s="0">
-        <v>0.249905252868173</v>
+        <v>-0.053881941699784996</v>
       </c>
       <c r="DH8" s="0">
-        <v>3.4171880271091299</v>
+        <v>0.74986382109320204</v>
       </c>
       <c r="DI8" s="0">
-        <v>9434072923105.2305</v>
+        <v>0.61431743452065091</v>
       </c>
     </row>
     <row r="9">
@@ -3673,40 +3673,40 @@
         <v>0.61866824801365095</v>
       </c>
       <c r="CX9" s="0">
-        <v>0.12960992129295101</v>
+        <v>0.129609932485519</v>
       </c>
       <c r="CY9" s="0">
-        <v>0.24999746537279499</v>
+        <v>0.74977400789802695</v>
       </c>
       <c r="CZ9" s="0">
-        <v>0.87529898156397501</v>
+        <v>0.87529899990990501</v>
       </c>
       <c r="DA9" s="0">
-        <v>0.22935809120817</v>
+        <v>0.22936153257077899</v>
       </c>
       <c r="DB9" s="0">
-        <v>0.40469515680122697</v>
+        <v>0.65165740736606304</v>
       </c>
       <c r="DC9" s="0">
-        <v>0.70972475740239704</v>
+        <v>0.70973844951202403</v>
       </c>
       <c r="DD9" s="0">
-        <v>0.18686311395156399</v>
+        <v>0.18687960171707699</v>
       </c>
       <c r="DE9" s="0">
-        <v>0.18325384871039399</v>
+        <v>0.75003367036566504</v>
       </c>
       <c r="DF9" s="0">
-        <v>0.85047221985509303</v>
+        <v>0.85048484784663003</v>
       </c>
       <c r="DG9" s="0">
-        <v>-0.12038754407984398</v>
+        <v>-0.62016407541250795</v>
       </c>
       <c r="DH9" s="0">
-        <v>-0.17533706559305698</v>
+        <v>-0.42229587479528408</v>
       </c>
       <c r="DI9" s="0">
-        <v>0.003609265241170001</v>
+        <v>-0.56315406864858808</v>
       </c>
     </row>
     <row r="10">
@@ -4014,40 +4014,40 @@
         <v>0.90424413477533405</v>
       </c>
       <c r="CX10" s="0">
-        <v>8.8114300770314295e-09</v>
+        <v>4.4052836417970901e-08</v>
       </c>
       <c r="CY10" s="0">
-        <v>0.254744830617538</v>
+        <v>0.72740860631915705</v>
       </c>
       <c r="CZ10" s="0">
-        <v>2.0229475769395302</v>
+        <v>2.0229480582932902</v>
       </c>
       <c r="DA10" s="0">
-        <v>-0.49245714188780099</v>
+        <v>1.3939360037888201e-07</v>
       </c>
       <c r="DB10" s="0">
-        <v>-0.75553161103769295</v>
+        <v>0.73997842809192804</v>
       </c>
       <c r="DC10" s="0">
-        <v>1.64328394920224</v>
+        <v>2.0229480037968299</v>
       </c>
       <c r="DD10" s="0">
-        <v>-0.137647647638483</v>
+        <v>1.8279314625486201e-07</v>
       </c>
       <c r="DE10" s="0">
-        <v>-2.07506836932003</v>
+        <v>0.75420496552433702</v>
       </c>
       <c r="DF10" s="0">
-        <v>1.5974693853615201</v>
+        <v>2.02294840404684</v>
       </c>
       <c r="DG10" s="0">
-        <v>-0.25474482180610791</v>
+        <v>-0.72740856226632067</v>
       </c>
       <c r="DH10" s="0">
-        <v>0.26307446914989197</v>
+        <v>-0.73997828869832771</v>
       </c>
       <c r="DI10" s="0">
-        <v>1.9374207216815471</v>
+        <v>-0.75420478273119074</v>
       </c>
     </row>
     <row r="11">
@@ -4355,40 +4355,40 @@
         <v>0.19553423638168599</v>
       </c>
       <c r="CX11" s="0">
-        <v>2.2894359655331701e-08</v>
+        <v>2.30445503006963e-08</v>
       </c>
       <c r="CY11" s="0">
-        <v>0.246338955764657</v>
+        <v>0.64164273869541699</v>
       </c>
       <c r="CZ11" s="0">
-        <v>0.88857847434312298</v>
+        <v>0.88857804990725697</v>
       </c>
       <c r="DA11" s="0">
-        <v>-0.52412416079120105</v>
+        <v>2.73779270002803e-07</v>
       </c>
       <c r="DB11" s="0">
-        <v>-0.19070617989011501</v>
+        <v>0.64390596992786497</v>
       </c>
       <c r="DC11" s="0">
-        <v>0.65638468787789594</v>
+        <v>0.88857839923021698</v>
       </c>
       <c r="DD11" s="0">
-        <v>-0.034932318849057599</v>
+        <v>1.20706725763027e-07</v>
       </c>
       <c r="DE11" s="0">
-        <v>-0.84435354041022004</v>
+        <v>0.64900251219054395</v>
       </c>
       <c r="DF11" s="0">
-        <v>0.82618045744234403</v>
+        <v>0.88857820825383005</v>
       </c>
       <c r="DG11" s="0">
-        <v>-0.24633893287029734</v>
+        <v>-0.64164271565086672</v>
       </c>
       <c r="DH11" s="0">
-        <v>-0.33341798090108604</v>
+        <v>-0.64390569614859494</v>
       </c>
       <c r="DI11" s="0">
-        <v>0.80942122156116247</v>
+        <v>-0.64900239148381822</v>
       </c>
     </row>
     <row r="12">
@@ -4696,40 +4696,40 @@
         <v>-0.30222177514313697</v>
       </c>
       <c r="CX12" s="0">
-        <v>7.5163280974983394e-08</v>
+        <v>3.7581493257582901e-07</v>
       </c>
       <c r="CY12" s="0">
-        <v>0.25921821412638202</v>
+        <v>0.68542821525213005</v>
       </c>
       <c r="CZ12" s="0">
-        <v>0.52367082211496196</v>
+        <v>0.52367077572008203</v>
       </c>
       <c r="DA12" s="0">
-        <v>-0.48443691129879801</v>
+        <v>1.7590962965583699e-07</v>
       </c>
       <c r="DB12" s="0">
-        <v>-0.064972143414759001</v>
+        <v>0.69449302505466504</v>
       </c>
       <c r="DC12" s="0">
-        <v>0.40839073422967898</v>
+        <v>0.52367070100936497</v>
       </c>
       <c r="DD12" s="0">
-        <v>-0.068333346616979707</v>
+        <v>1.3620310610974199e-07</v>
       </c>
       <c r="DE12" s="0">
-        <v>-0.093229677405088904</v>
+        <v>0.69915655628280005</v>
       </c>
       <c r="DF12" s="0">
-        <v>0.46555571793300898</v>
+        <v>0.52367076921758304</v>
       </c>
       <c r="DG12" s="0">
-        <v>-0.25921813896310103</v>
+        <v>-0.68542783943719743</v>
       </c>
       <c r="DH12" s="0">
-        <v>-0.41946476788403902</v>
+        <v>-0.6944928491450354</v>
       </c>
       <c r="DI12" s="0">
-        <v>0.024896330788109197</v>
+        <v>-0.69915642007969392</v>
       </c>
     </row>
     <row r="13">
@@ -5027,40 +5027,40 @@
         <v>0.69444679007842902</v>
       </c>
       <c r="CX13" s="0">
-        <v>3.2366666370707699e-09</v>
+        <v>1.5952673059291501e-08</v>
       </c>
       <c r="CY13" s="0">
-        <v>0.38135027967826801</v>
+        <v>0.75000000000060596</v>
       </c>
       <c r="CZ13" s="0">
-        <v>19.1021060323325</v>
+        <v>18.896257422988299</v>
       </c>
       <c r="DA13" s="0">
-        <v>-0.0291832758410164</v>
+        <v>2.4852722597534599e-10</v>
       </c>
       <c r="DB13" s="0">
-        <v>-57.180692490296302</v>
+        <v>0.48458125813066499</v>
       </c>
       <c r="DC13" s="0">
-        <v>28.306542874514999</v>
+        <v>40.197494988897297</v>
       </c>
       <c r="DD13" s="0">
-        <v>-0.0864898289756732</v>
+        <v>2.79598968279515e-07</v>
       </c>
       <c r="DE13" s="0">
-        <v>-12.5542870448838</v>
+        <v>0.824263607421995</v>
       </c>
       <c r="DF13" s="0">
-        <v>7.4379126338683701</v>
+        <v>21.264634797497902</v>
       </c>
       <c r="DG13" s="0">
-        <v>-0.38135027644160135</v>
+        <v>-0.74999998404793289</v>
       </c>
       <c r="DH13" s="0">
-        <v>57.151509214455288</v>
+        <v>-0.48458125788213779</v>
       </c>
       <c r="DI13" s="0">
-        <v>12.467797215908128</v>
+        <v>-0.82426332782302669</v>
       </c>
     </row>
     <row r="14">
@@ -5368,40 +5368,40 @@
         <v>0.55301031282352597</v>
       </c>
       <c r="CX14" s="0">
-        <v>0.099369123807290793</v>
+        <v>0.099369137579821507</v>
       </c>
       <c r="CY14" s="0">
-        <v>0.25020579781635899</v>
+        <v>0.75003007585132697</v>
       </c>
       <c r="CZ14" s="0">
-        <v>0.85378316176425195</v>
+        <v>0.85378320632976701</v>
       </c>
       <c r="DA14" s="0">
-        <v>0.394455976188406</v>
+        <v>0.39444564835421803</v>
       </c>
       <c r="DB14" s="0">
-        <v>-0.42483399305281599</v>
+        <v>0.66583519730026797</v>
       </c>
       <c r="DC14" s="0">
-        <v>0.96265663167167903</v>
+        <v>0.96267102491982404</v>
       </c>
       <c r="DD14" s="0">
-        <v>0.62534591698731401</v>
+        <v>0.62537863206203803</v>
       </c>
       <c r="DE14" s="0">
-        <v>-0.59813917580603704</v>
+        <v>0.77253513419193598</v>
       </c>
       <c r="DF14" s="0">
-        <v>1.61317067211684</v>
+        <v>1.61318182695495</v>
       </c>
       <c r="DG14" s="0">
-        <v>-0.15083667400906819</v>
+        <v>-0.65066093827150551</v>
       </c>
       <c r="DH14" s="0">
-        <v>0.81928996924122199</v>
+        <v>-0.27138954894604994</v>
       </c>
       <c r="DI14" s="0">
-        <v>1.2234850927933509</v>
+        <v>-0.14715650212989795</v>
       </c>
     </row>
     <row r="15">
@@ -5709,40 +5709,40 @@
         <v>0.18911784168696699</v>
       </c>
       <c r="CX15" s="0">
-        <v>0.14818349902867101</v>
+        <v>0.74387808732830096</v>
       </c>
       <c r="CY15" s="0">
-        <v>0.24332873567881799</v>
+        <v>0.803851400593247</v>
       </c>
       <c r="CZ15" s="0">
-        <v>1.98150711380461e-08</v>
+        <v>2.4378440275216903e-07</v>
       </c>
       <c r="DA15" s="0">
-        <v>0.69227733568737904</v>
+        <v>0.54273661573682896</v>
       </c>
       <c r="DB15" s="0">
-        <v>0.094512907969787202</v>
+        <v>0.74679975215026295</v>
       </c>
       <c r="DC15" s="0">
-        <v>-0.32098746517533699</v>
+        <v>6.8700431758582102e-08</v>
       </c>
       <c r="DD15" s="0">
-        <v>7380264246505.4404</v>
+        <v>0.67098406731390503</v>
       </c>
       <c r="DE15" s="0">
-        <v>-7761586541254.1797</v>
+        <v>0.74865830007288203</v>
       </c>
       <c r="DF15" s="0">
-        <v>-0.38644615306696101</v>
+        <v>9.5357155324614397e-08</v>
       </c>
       <c r="DG15" s="0">
-        <v>-0.095145236650146986</v>
+        <v>-0.059973313264946038</v>
       </c>
       <c r="DH15" s="0">
-        <v>0.59776442771759186</v>
+        <v>-0.20406313641343399</v>
       </c>
       <c r="DI15" s="0">
-        <v>15141850787759.621</v>
+        <v>-0.077674232758977002</v>
       </c>
     </row>
     <row r="16">
@@ -6050,40 +6050,40 @@
         <v>0.61536111108184099</v>
       </c>
       <c r="CX16" s="0">
-        <v>0.25264814862871698</v>
+        <v>0.25264816119067302</v>
       </c>
       <c r="CY16" s="0">
-        <v>0.24969126765848501</v>
+        <v>0.74518863868254204</v>
       </c>
       <c r="CZ16" s="0">
-        <v>0.88309694577479003</v>
+        <v>0.88309686899167805</v>
       </c>
       <c r="DA16" s="0">
-        <v>0.78863736870609602</v>
+        <v>0.78858873503708704</v>
       </c>
       <c r="DB16" s="0">
-        <v>-0.70420897103746005</v>
+        <v>0.72978216408624597</v>
       </c>
       <c r="DC16" s="0">
-        <v>1.1249286863901999</v>
+        <v>1.1249407048292299</v>
       </c>
       <c r="DD16" s="0">
-        <v>1.45271219237041</v>
+        <v>1.45269810595625</v>
       </c>
       <c r="DE16" s="0">
-        <v>-0.95580412397595604</v>
+        <v>0.75060382105502099</v>
       </c>
       <c r="DF16" s="0">
-        <v>2.48279458540354</v>
+        <v>2.4827981779582702</v>
       </c>
       <c r="DG16" s="0">
-        <v>0.0029568809702319732</v>
+        <v>-0.49254047749186902</v>
       </c>
       <c r="DH16" s="0">
-        <v>1.4928463397435561</v>
+        <v>0.058806570950841075</v>
       </c>
       <c r="DI16" s="0">
-        <v>2.4085163163463661</v>
+        <v>0.70209428490122905</v>
       </c>
     </row>
     <row r="17">
@@ -6391,40 +6391,40 @@
         <v>0.97451638479506297</v>
       </c>
       <c r="CX17" s="0">
-        <v>0.16204712145837599</v>
+        <v>0.16204711558815199</v>
       </c>
       <c r="CY17" s="0">
-        <v>0.24997920264567899</v>
+        <v>0.750219816557403</v>
       </c>
       <c r="CZ17" s="0">
-        <v>1.7268036992504701</v>
+        <v>1.72680396540338</v>
       </c>
       <c r="DA17" s="0">
-        <v>0.51356261652556601</v>
+        <v>0.51356929311049604</v>
       </c>
       <c r="DB17" s="0">
-        <v>-0.637078354499658</v>
+        <v>0.76858832430716495</v>
       </c>
       <c r="DC17" s="0">
-        <v>1.7464275928073001</v>
+        <v>1.7464004779098099</v>
       </c>
       <c r="DD17" s="0">
-        <v>0.47244825673496599</v>
+        <v>0.47245114192401899</v>
       </c>
       <c r="DE17" s="0">
-        <v>-0.77568479621090702</v>
+        <v>0.78019460539242202</v>
       </c>
       <c r="DF17" s="0">
-        <v>2.1891460491451098</v>
+        <v>2.1891304252883299</v>
       </c>
       <c r="DG17" s="0">
-        <v>-0.087932081187303002</v>
+        <v>-0.58817270096925101</v>
       </c>
       <c r="DH17" s="0">
-        <v>1.1506409710252239</v>
+        <v>-0.25501903119666891</v>
       </c>
       <c r="DI17" s="0">
-        <v>1.248133052945873</v>
+        <v>-0.30774346346840303</v>
       </c>
     </row>
     <row r="18">
@@ -6732,40 +6732,40 @@
         <v>0.32079780401024999</v>
       </c>
       <c r="CX18" s="0">
-        <v>7.3668412816490599e-09</v>
+        <v>7.3671850440461898e-09</v>
       </c>
       <c r="CY18" s="0">
-        <v>0.22837573780943901</v>
+        <v>0.69746763625818897</v>
       </c>
       <c r="CZ18" s="0">
-        <v>1.56262011894473</v>
+        <v>1.56262260675607</v>
       </c>
       <c r="DA18" s="0">
-        <v>-1.2523020839005301</v>
+        <v>2.3611085994004899e-08</v>
       </c>
       <c r="DB18" s="0">
-        <v>-0.072326420357909593</v>
+        <v>0.68886063462698499</v>
       </c>
       <c r="DC18" s="0">
-        <v>1.09526805556587</v>
+        <v>1.56262287528355</v>
       </c>
       <c r="DD18" s="0">
-        <v>-0.249999999075737</v>
+        <v>9.6433815132160095e-08</v>
       </c>
       <c r="DE18" s="0">
-        <v>-1.1060898485352599</v>
+        <v>0.75686635236947197</v>
       </c>
       <c r="DF18" s="0">
-        <v>1.2082639065176299</v>
+        <v>1.56262431488816</v>
       </c>
       <c r="DG18" s="0">
-        <v>-0.22837573044259774</v>
+        <v>-0.69746762889100389</v>
       </c>
       <c r="DH18" s="0">
-        <v>-1.1799756635426206</v>
+        <v>-0.68886061101589902</v>
       </c>
       <c r="DI18" s="0">
-        <v>0.85608984945952293</v>
+        <v>-0.75686625593565682</v>
       </c>
     </row>
     <row r="19">
@@ -7073,40 +7073,40 @@
         <v>0.54227878163324195</v>
       </c>
       <c r="CX19" s="0">
-        <v>0.013163271077651899</v>
+        <v>0.0131633310359262</v>
       </c>
       <c r="CY19" s="0">
-        <v>0.25002778683411703</v>
+        <v>0.750124776678736</v>
       </c>
       <c r="CZ19" s="0">
-        <v>1.16208922494881</v>
+        <v>1.1620894362469201</v>
       </c>
       <c r="DA19" s="0">
-        <v>0.14674867880817799</v>
+        <v>0.146749889747993</v>
       </c>
       <c r="DB19" s="0">
-        <v>-0.746651937189453</v>
+        <v>0.74921898214591298</v>
       </c>
       <c r="DC19" s="0">
-        <v>1.30183937260886</v>
+        <v>1.30182613088739</v>
       </c>
       <c r="DD19" s="0">
-        <v>0.233682362194818</v>
+        <v>0.233687705058581</v>
       </c>
       <c r="DE19" s="0">
-        <v>-3.1015192597007801</v>
+        <v>0.75234747130711199</v>
       </c>
       <c r="DF19" s="0">
-        <v>1.72887586005814</v>
+        <v>1.7288572382621601</v>
       </c>
       <c r="DG19" s="0">
-        <v>-0.23686451575646514</v>
+        <v>-0.73696144564280985</v>
       </c>
       <c r="DH19" s="0">
-        <v>0.89340061599763099</v>
+        <v>-0.60246909239792001</v>
       </c>
       <c r="DI19" s="0">
-        <v>3.3352016218955982</v>
+        <v>-0.51865976624853105</v>
       </c>
     </row>
     <row r="20">
@@ -7414,40 +7414,40 @@
         <v>0.68797226311590198</v>
       </c>
       <c r="CX20" s="0">
-        <v>0.061235908771062997</v>
+        <v>0.0612359156536008</v>
       </c>
       <c r="CY20" s="0">
-        <v>0.24999422723015999</v>
+        <v>0.74979097024663799</v>
       </c>
       <c r="CZ20" s="0">
-        <v>1.5336188048969599</v>
+        <v>1.5336188997757401</v>
       </c>
       <c r="DA20" s="0">
-        <v>0.22530215033141199</v>
+        <v>0.225302708158962</v>
       </c>
       <c r="DB20" s="0">
-        <v>0.293532373914624</v>
+        <v>0.749756915917422</v>
       </c>
       <c r="DC20" s="0">
-        <v>1.61131768915371</v>
+        <v>1.6113208755564501</v>
       </c>
       <c r="DD20" s="0">
-        <v>0.27689351555851199</v>
+        <v>0.27689334615946698</v>
       </c>
       <c r="DE20" s="0">
-        <v>-1.2452092440552101</v>
+        <v>0.749979194487019</v>
       </c>
       <c r="DF20" s="0">
-        <v>2.3988502334597599</v>
+        <v>2.3988802508237601</v>
       </c>
       <c r="DG20" s="0">
-        <v>-0.18875831845909699</v>
+        <v>-0.68855505459303723</v>
       </c>
       <c r="DH20" s="0">
-        <v>-0.068230223583212013</v>
+        <v>-0.52445420775845997</v>
       </c>
       <c r="DI20" s="0">
-        <v>1.522102759613722</v>
+        <v>-0.47308584832755202</v>
       </c>
     </row>
     <row r="21">
@@ -7755,40 +7755,40 @@
         <v>-0.260904193221007</v>
       </c>
       <c r="CX21" s="0">
-        <v>0.499999960228247</v>
+        <v>1.4999999835413</v>
       </c>
       <c r="CY21" s="0">
-        <v>0.249957577103644</v>
+        <v>0.76192610033235597</v>
       </c>
       <c r="CZ21" s="0">
-        <v>0.475242287308902</v>
+        <v>0.32765817680627701</v>
       </c>
       <c r="DA21" s="0">
-        <v>-21.344098297475899</v>
+        <v>1.49999997576834</v>
       </c>
       <c r="DB21" s="0">
-        <v>23.876576938506101</v>
+        <v>0.76278226756298095</v>
       </c>
       <c r="DC21" s="0">
-        <v>-0.047859753450036797</v>
+        <v>0.51156264318104405</v>
       </c>
       <c r="DD21" s="0">
-        <v>-0.25014273721628699</v>
+        <v>1.4999989652484</v>
       </c>
       <c r="DE21" s="0">
-        <v>0.30038264576331503</v>
+        <v>0.74597952017370295</v>
       </c>
       <c r="DF21" s="0">
-        <v>-0.40529558839172503</v>
+        <v>0.28269548592272697</v>
       </c>
       <c r="DG21" s="0">
-        <v>0.25004238312460303</v>
+        <v>0.73807388320894407</v>
       </c>
       <c r="DH21" s="0">
-        <v>-45.220675235982</v>
+        <v>0.73721770820535903</v>
       </c>
       <c r="DI21" s="0">
-        <v>-0.55052538297960196</v>
+        <v>0.75401944507469709</v>
       </c>
     </row>
     <row r="22">
@@ -8096,40 +8096,40 @@
         <v>0.87092074870949998</v>
       </c>
       <c r="CX22" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY22" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ22" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA22" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB22" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC22" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD22" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE22" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF22" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG22" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH22" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI22" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="23">
@@ -8437,40 +8437,40 @@
         <v>0.79050781324358599</v>
       </c>
       <c r="CX23" s="0">
-        <v>0.051006854424783601</v>
+        <v>0.051006884347871699</v>
       </c>
       <c r="CY23" s="0">
-        <v>0.24975186133840799</v>
+        <v>0.75004780102420299</v>
       </c>
       <c r="CZ23" s="0">
-        <v>0.836883528582689</v>
+        <v>0.83688345300962197</v>
       </c>
       <c r="DA23" s="0">
-        <v>0.26109530892498101</v>
+        <v>0.26110064455349002</v>
       </c>
       <c r="DB23" s="0">
-        <v>0.43431000430575101</v>
+        <v>0.70015767517406302</v>
       </c>
       <c r="DC23" s="0">
-        <v>0.93551389494568404</v>
+        <v>0.93554060789458904</v>
       </c>
       <c r="DD23" s="0">
-        <v>0.65644446435420201</v>
+        <v>0.65641664071680095</v>
       </c>
       <c r="DE23" s="0">
-        <v>1.2374747338571099</v>
+        <v>0.75767539834301501</v>
       </c>
       <c r="DF23" s="0">
-        <v>1.42359085252006</v>
+        <v>1.4235793853903</v>
       </c>
       <c r="DG23" s="0">
-        <v>-0.1987450069136244</v>
+        <v>-0.69904091667633128</v>
       </c>
       <c r="DH23" s="0">
-        <v>-0.17321469538077</v>
+        <v>-0.439057030620573</v>
       </c>
       <c r="DI23" s="0">
-        <v>-0.58103026950290793</v>
+        <v>-0.10125875762621406</v>
       </c>
     </row>
     <row r="24">
@@ -8778,40 +8778,40 @@
         <v>0.74284057261265601</v>
       </c>
       <c r="CX24" s="0">
-        <v>0.078005419765296</v>
+        <v>0.078005432139063205</v>
       </c>
       <c r="CY24" s="0">
-        <v>0.24986209848354299</v>
+        <v>0.74362462446794197</v>
       </c>
       <c r="CZ24" s="0">
-        <v>0.996871731590939</v>
+        <v>0.99687179239315804</v>
       </c>
       <c r="DA24" s="0">
-        <v>0.34555020308464002</v>
+        <v>0.34556709438600802</v>
       </c>
       <c r="DB24" s="0">
-        <v>-0.37164587848891001</v>
+        <v>0.75006361638920904</v>
       </c>
       <c r="DC24" s="0">
-        <v>1.1570089501730001</v>
+        <v>1.1569694897946099</v>
       </c>
       <c r="DD24" s="0">
-        <v>0.60228337290994205</v>
+        <v>0.602263339953376</v>
       </c>
       <c r="DE24" s="0">
-        <v>-0.13610888600001</v>
+        <v>0.78920073325850004</v>
       </c>
       <c r="DF24" s="0">
-        <v>1.87933202579326</v>
+        <v>1.87934072970753</v>
       </c>
       <c r="DG24" s="0">
-        <v>-0.171856678718247</v>
+        <v>-0.66561919232887878</v>
       </c>
       <c r="DH24" s="0">
-        <v>0.71719608157355008</v>
+        <v>-0.40449652200320102</v>
       </c>
       <c r="DI24" s="0">
-        <v>0.73839225890995208</v>
+        <v>-0.18693739330512404</v>
       </c>
     </row>
     <row r="25">
@@ -9119,40 +9119,40 @@
         <v>1.27913973282473</v>
       </c>
       <c r="CX25" s="0">
-        <v>0.171231427417989</v>
+        <v>0.17123142816567999</v>
       </c>
       <c r="CY25" s="0">
-        <v>0.25093187814905599</v>
+        <v>0.74982292563311803</v>
       </c>
       <c r="CZ25" s="0">
-        <v>1.2021202646554801</v>
+        <v>1.2021202494840999</v>
       </c>
       <c r="DA25" s="0">
-        <v>0.601379473069654</v>
+        <v>0.60139701461621298</v>
       </c>
       <c r="DB25" s="0">
-        <v>-0.57310625151514805</v>
+        <v>0.75589796515111696</v>
       </c>
       <c r="DC25" s="0">
-        <v>1.52164050885527</v>
+        <v>1.52165752537771</v>
       </c>
       <c r="DD25" s="0">
-        <v>0.90840139555822996</v>
+        <v>0.90839905560329504</v>
       </c>
       <c r="DE25" s="0">
-        <v>-1.0061684223038401</v>
+        <v>0.74569510682196705</v>
       </c>
       <c r="DF25" s="0">
-        <v>2.6933958569320602</v>
+        <v>2.6933652288666901</v>
       </c>
       <c r="DG25" s="0">
-        <v>-0.079700450731066991</v>
+        <v>-0.57859149746743799</v>
       </c>
       <c r="DH25" s="0">
-        <v>1.1744857245848022</v>
+        <v>-0.15450095053490398</v>
       </c>
       <c r="DI25" s="0">
-        <v>1.91456981786207</v>
+        <v>0.16270394878132799</v>
       </c>
     </row>
     <row r="26">
@@ -9460,40 +9460,40 @@
         <v>1.0843653929630299</v>
       </c>
       <c r="CX26" s="0">
-        <v>0.049133744525234099</v>
+        <v>0.049133743756610303</v>
       </c>
       <c r="CY26" s="0">
-        <v>0.24931128951283499</v>
+        <v>0.76981014011691196</v>
       </c>
       <c r="CZ26" s="0">
-        <v>2.2159223463672202</v>
+        <v>2.2159223794415501</v>
       </c>
       <c r="DA26" s="0">
-        <v>0.14946834258153499</v>
+        <v>0.149468680337557</v>
       </c>
       <c r="DB26" s="0">
-        <v>-0.53164269602202996</v>
+        <v>0.75001568564908205</v>
       </c>
       <c r="DC26" s="0">
-        <v>2.1724906011217699</v>
+        <v>2.1724477713288599</v>
       </c>
       <c r="DD26" s="0">
-        <v>0.165585640128774</v>
+        <v>0.16558488599145599</v>
       </c>
       <c r="DE26" s="0">
-        <v>-2.6473543449970398</v>
+        <v>0.75899775803842995</v>
       </c>
       <c r="DF26" s="0">
-        <v>2.7658602161544801</v>
+        <v>2.7658410065181398</v>
       </c>
       <c r="DG26" s="0">
-        <v>-0.20017754498760088</v>
+        <v>-0.72067639636030167</v>
       </c>
       <c r="DH26" s="0">
-        <v>0.68111103860356492</v>
+        <v>-0.60054700531152505</v>
       </c>
       <c r="DI26" s="0">
-        <v>2.8129399851258139</v>
+        <v>-0.59341287204697402</v>
       </c>
     </row>
     <row r="27">
@@ -9801,40 +9801,40 @@
         <v>0.69245130557771695</v>
       </c>
       <c r="CX27" s="0">
-        <v>6.5297233507041002e-09</v>
+        <v>6.5293568152999798e-09</v>
       </c>
       <c r="CY27" s="0">
-        <v>0.24852820164897901</v>
+        <v>0.69398080502041104</v>
       </c>
       <c r="CZ27" s="0">
-        <v>1.5874006539995</v>
+        <v>1.58740096354192</v>
       </c>
       <c r="DA27" s="0">
-        <v>-0.91681932817594203</v>
+        <v>5.1667927837178696e-09</v>
       </c>
       <c r="DB27" s="0">
-        <v>-0.55152342271786403</v>
+        <v>0.56233882018185799</v>
       </c>
       <c r="DC27" s="0">
-        <v>1.1313071340013701</v>
+        <v>1.5874009536806499</v>
       </c>
       <c r="DD27" s="0">
-        <v>-0.204114136285235</v>
+        <v>4.7777422346794599e-09</v>
       </c>
       <c r="DE27" s="0">
-        <v>-1.0208018020185801</v>
+        <v>0.58738199020821802</v>
       </c>
       <c r="DF27" s="0">
-        <v>1.0958694169645999</v>
+        <v>1.58740087547333</v>
       </c>
       <c r="DG27" s="0">
-        <v>-0.24852819511925567</v>
+        <v>-0.69398079849105421</v>
       </c>
       <c r="DH27" s="0">
-        <v>-0.365295905458078</v>
+        <v>-0.56233881501506522</v>
       </c>
       <c r="DI27" s="0">
-        <v>0.81668766573334506</v>
+        <v>-0.58738198543047582</v>
       </c>
     </row>
     <row r="28">
@@ -10132,40 +10132,40 @@
         <v>0.80579620406805597</v>
       </c>
       <c r="CX28" s="0">
-        <v>6.7363493809431397e-09</v>
+        <v>6.7363492726379502e-09</v>
       </c>
       <c r="CY28" s="0">
-        <v>0.24983152814413501</v>
+        <v>0.71791341177232304</v>
       </c>
       <c r="CZ28" s="0">
-        <v>1.79395645789696</v>
+        <v>1.7939565610414001</v>
       </c>
       <c r="DA28" s="0">
-        <v>-0.67439516201426297</v>
+        <v>1.17013053289614e-07</v>
       </c>
       <c r="DB28" s="0">
-        <v>-0.37722753165425399</v>
+        <v>0.67065160999227802</v>
       </c>
       <c r="DC28" s="0">
-        <v>1.3748286878465801</v>
+        <v>1.7939555383224499</v>
       </c>
       <c r="DD28" s="0">
-        <v>-0.233098560134434</v>
+        <v>1.0879324474347e-07</v>
       </c>
       <c r="DE28" s="0">
-        <v>-1.20154899460192</v>
+        <v>0.63325764730259204</v>
       </c>
       <c r="DF28" s="0">
-        <v>1.23857277886647</v>
+        <v>1.79395695864961</v>
       </c>
       <c r="DG28" s="0">
-        <v>-0.24983152140778564</v>
+        <v>-0.71791340503597378</v>
       </c>
       <c r="DH28" s="0">
-        <v>-0.29716763036000898</v>
+        <v>-0.67065149297922477</v>
       </c>
       <c r="DI28" s="0">
-        <v>0.96845043446748602</v>
+        <v>-0.6332575385093473</v>
       </c>
     </row>
     <row r="29">
@@ -10473,40 +10473,40 @@
         <v>0.37082720137791902</v>
       </c>
       <c r="CX29" s="0">
-        <v>5.7791848190054401e-09</v>
+        <v>5.77955831579689e-09</v>
       </c>
       <c r="CY29" s="0">
-        <v>0.25096767952907001</v>
+        <v>0.72649680854891996</v>
       </c>
       <c r="CZ29" s="0">
-        <v>2.1815823965894601</v>
+        <v>2.1815822022548002</v>
       </c>
       <c r="DA29" s="0">
-        <v>-0.41146526762698299</v>
+        <v>9.9193866419321594e-08</v>
       </c>
       <c r="DB29" s="0">
-        <v>-0.43275109679158102</v>
+        <v>0.740068235893791</v>
       </c>
       <c r="DC29" s="0">
-        <v>1.7679157000674599</v>
+        <v>2.18158258172289</v>
       </c>
       <c r="DD29" s="0">
-        <v>-0.20045544884111799</v>
+        <v>8.5693970261752196e-08</v>
       </c>
       <c r="DE29" s="0">
-        <v>-1.94895600808901</v>
+        <v>0.758512830999721</v>
       </c>
       <c r="DF29" s="0">
-        <v>1.6142179623667801</v>
+        <v>2.1815828151301102</v>
       </c>
       <c r="DG29" s="0">
-        <v>-0.25096767374988521</v>
+        <v>-0.72649680276936168</v>
       </c>
       <c r="DH29" s="0">
-        <v>0.021285829164598036</v>
+        <v>-0.74006813669992455</v>
       </c>
       <c r="DI29" s="0">
-        <v>1.7485005592478919</v>
+        <v>-0.75851274530575075</v>
       </c>
     </row>
     <row r="30">
@@ -10814,40 +10814,40 @@
         <v>0.77234333364423502</v>
       </c>
       <c r="CX30" s="0">
-        <v>5.8206426998213603e-09</v>
+        <v>1.6494998014038299e-07</v>
       </c>
       <c r="CY30" s="0">
-        <v>0.35406011282662597</v>
+        <v>0.74998635154729298</v>
       </c>
       <c r="CZ30" s="0">
-        <v>19.5712942991379</v>
+        <v>17.320417932444101</v>
       </c>
       <c r="DA30" s="0">
-        <v>-0.017166951499471599</v>
+        <v>3.8502878033290298e-07</v>
       </c>
       <c r="DB30" s="0">
-        <v>-22.6999890749054</v>
+        <v>0.75000545510066396</v>
       </c>
       <c r="DC30" s="0">
-        <v>28.267659571909999</v>
+        <v>17.3148924716698</v>
       </c>
       <c r="DD30" s="0">
-        <v>-0.00064585202881470803</v>
+        <v>7.0267567775860404e-08</v>
       </c>
       <c r="DE30" s="0">
-        <v>-701.620264702957</v>
+        <v>0.76871867035260799</v>
       </c>
       <c r="DF30" s="0">
-        <v>725.51297207615198</v>
+        <v>18.9744337063036</v>
       </c>
       <c r="DG30" s="0">
-        <v>-0.35406010700598328</v>
+        <v>-0.74998618659731286</v>
       </c>
       <c r="DH30" s="0">
-        <v>22.682822123405927</v>
+        <v>-0.75000507007188366</v>
       </c>
       <c r="DI30" s="0">
-        <v>701.61961885092819</v>
+        <v>-0.76871860008504023</v>
       </c>
     </row>
     <row r="31">
@@ -11155,40 +11155,40 @@
         <v>0.72085726798015004</v>
       </c>
       <c r="CX31" s="0">
-        <v>0.13935902729903801</v>
+        <v>0.13935902592309601</v>
       </c>
       <c r="CY31" s="0">
-        <v>0.250046903471766</v>
+        <v>0.75348126892574696</v>
       </c>
       <c r="CZ31" s="0">
-        <v>1.5711362374642199</v>
+        <v>1.5711363177374</v>
       </c>
       <c r="DA31" s="0">
-        <v>0.49257689634470297</v>
+        <v>0.49257059571853201</v>
       </c>
       <c r="DB31" s="0">
-        <v>-0.722396110837914</v>
+        <v>0.774024768205678</v>
       </c>
       <c r="DC31" s="0">
-        <v>1.8432606597841401</v>
+        <v>1.8432487541757001</v>
       </c>
       <c r="DD31" s="0">
-        <v>0.47140851115416399</v>
+        <v>0.47140794632768201</v>
       </c>
       <c r="DE31" s="0">
-        <v>-2.78862471442066</v>
+        <v>0.83083723126042497</v>
       </c>
       <c r="DF31" s="0">
-        <v>2.1977957098272398</v>
+        <v>2.1978169809861701</v>
       </c>
       <c r="DG31" s="0">
-        <v>-0.11068787617272799</v>
+        <v>-0.61412224300265095</v>
       </c>
       <c r="DH31" s="0">
-        <v>1.214973007182617</v>
+        <v>-0.28145417248714599</v>
       </c>
       <c r="DI31" s="0">
-        <v>3.2600332255748241</v>
+        <v>-0.35942928493274295</v>
       </c>
     </row>
     <row r="32">
@@ -11496,40 +11496,40 @@
         <v>0.061852059590029602</v>
       </c>
       <c r="CX32" s="0">
-        <v>6.7574358849660301e-09</v>
+        <v>6.7870518567598703e-09</v>
       </c>
       <c r="CY32" s="0">
-        <v>0.23290135742735499</v>
+        <v>0.55254629579725301</v>
       </c>
       <c r="CZ32" s="0">
-        <v>1.5328465811474701</v>
+        <v>1.5328463884967101</v>
       </c>
       <c r="DA32" s="0">
-        <v>-0.94472863270247898</v>
+        <v>2.1588898278662401e-08</v>
       </c>
       <c r="DB32" s="0">
-        <v>-0.43989694747401198</v>
+        <v>0.59767149880563997</v>
       </c>
       <c r="DC32" s="0">
-        <v>1.08479619692027</v>
+        <v>1.5328481246510599</v>
       </c>
       <c r="DD32" s="0">
-        <v>-0.206754711575799</v>
+        <v>4.9931702092665197e-07</v>
       </c>
       <c r="DE32" s="0">
-        <v>-0.91476029280943905</v>
+        <v>0.605293726555025</v>
       </c>
       <c r="DF32" s="0">
-        <v>1.03981739834625</v>
+        <v>1.5328501142356601</v>
       </c>
       <c r="DG32" s="0">
-        <v>-0.2329013506699191</v>
+        <v>-0.5525462890102012</v>
       </c>
       <c r="DH32" s="0">
-        <v>-0.504831685228467</v>
+        <v>-0.59767147721674174</v>
       </c>
       <c r="DI32" s="0">
-        <v>0.7080055812336401</v>
+        <v>-0.60529322723800405</v>
       </c>
     </row>
     <row r="33">
@@ -11837,40 +11837,40 @@
         <v>0.45835266544497899</v>
       </c>
       <c r="CX33" s="0">
-        <v>5.5543492925180101e-09</v>
+        <v>1.11081411512809e-09</v>
       </c>
       <c r="CY33" s="0">
-        <v>0.23331894349646301</v>
+        <v>0.74092980649498896</v>
       </c>
       <c r="CZ33" s="0">
-        <v>2.0445217952674102</v>
+        <v>2.0445212181933701</v>
       </c>
       <c r="DA33" s="0">
-        <v>-22.983485765721699</v>
+        <v>1.7298491824418099e-08</v>
       </c>
       <c r="DB33" s="0">
-        <v>23.041551398469402</v>
+        <v>0.73543923606995298</v>
       </c>
       <c r="DC33" s="0">
-        <v>1.4748313859139299</v>
+        <v>2.0445213537737299</v>
       </c>
       <c r="DD33" s="0">
-        <v>-0.24999999989575</v>
+        <v>3.5270034566143099e-08</v>
       </c>
       <c r="DE33" s="0">
-        <v>-2.1087860707097401</v>
+        <v>1.1770777762298299</v>
       </c>
       <c r="DF33" s="0">
-        <v>1.7737524188701099</v>
+        <v>2.0445199515104999</v>
       </c>
       <c r="DG33" s="0">
-        <v>-0.23331893794211372</v>
+        <v>-0.74092980538417486</v>
       </c>
       <c r="DH33" s="0">
-        <v>-46.025037164191104</v>
+        <v>-0.73543921877146112</v>
       </c>
       <c r="DI33" s="0">
-        <v>1.8587860708139901</v>
+        <v>-1.1770777409597952</v>
       </c>
     </row>
     <row r="34">
@@ -12178,40 +12178,40 @@
         <v>-0.36077039257180998</v>
       </c>
       <c r="CX34" s="0">
-        <v>9.4004441265420098e-09</v>
+        <v>9.4000068824264308e-09</v>
       </c>
       <c r="CY34" s="0">
-        <v>0.22487500154228199</v>
+        <v>0.38316617720290203</v>
       </c>
       <c r="CZ34" s="0">
-        <v>0.98730026133593096</v>
+        <v>0.98730073269903296</v>
       </c>
       <c r="DA34" s="0">
-        <v>-101.341723812995</v>
+        <v>2.81998361707054e-08</v>
       </c>
       <c r="DB34" s="0">
-        <v>52.33005002614</v>
+        <v>0.61978139256518605</v>
       </c>
       <c r="DC34" s="0">
-        <v>0.344171150170136</v>
+        <v>0.987300339899158</v>
       </c>
       <c r="DD34" s="0">
-        <v>-0.24999999931427599</v>
+        <v>8.2100230129924797e-08</v>
       </c>
       <c r="DE34" s="0">
-        <v>-0.159269492717628</v>
+        <v>0.53090421557189804</v>
       </c>
       <c r="DF34" s="0">
-        <v>0.77711370521396295</v>
+        <v>0.987300500291723</v>
       </c>
       <c r="DG34" s="0">
-        <v>-0.22487499214183787</v>
+        <v>-0.38316616780289514</v>
       </c>
       <c r="DH34" s="0">
-        <v>-153.671773839135</v>
+        <v>-0.61978136436534992</v>
       </c>
       <c r="DI34" s="0">
-        <v>-0.090730506596647997</v>
+        <v>-0.53090413347166787</v>
       </c>
     </row>
     <row r="35">
@@ -12519,40 +12519,40 @@
         <v>0.93060095506322105</v>
       </c>
       <c r="CX35" s="0">
-        <v>1.65382764161532e-07</v>
+        <v>1.6538275206145001e-07</v>
       </c>
       <c r="CY35" s="0">
-        <v>0.24944293206655499</v>
+        <v>0.74821756809908901</v>
       </c>
       <c r="CZ35" s="0">
-        <v>1.06872292659838</v>
+        <v>1.0687228556167601</v>
       </c>
       <c r="DA35" s="0">
-        <v>-0.064666447418001996</v>
+        <v>2.9157755007078498e-07</v>
       </c>
       <c r="DB35" s="0">
-        <v>0.61453499659247901</v>
+        <v>0.673946234024972</v>
       </c>
       <c r="DC35" s="0">
-        <v>1.0181543817676599</v>
+        <v>1.0687226822336999</v>
       </c>
       <c r="DD35" s="0">
-        <v>0.172792180028009</v>
+        <v>0.17279552263346201</v>
       </c>
       <c r="DE35" s="0">
-        <v>0.45813507530937198</v>
+        <v>0.73546413684169398</v>
       </c>
       <c r="DF35" s="0">
-        <v>1.5184217047967601</v>
+        <v>1.5184157208439499</v>
       </c>
       <c r="DG35" s="0">
-        <v>-0.24944276668379084</v>
+        <v>-0.74821740271633697</v>
       </c>
       <c r="DH35" s="0">
-        <v>-0.67920144401048099</v>
+        <v>-0.6739459424474219</v>
       </c>
       <c r="DI35" s="0">
-        <v>-0.28534289528136297</v>
+        <v>-0.562668614208232</v>
       </c>
     </row>
     <row r="36">
@@ -12860,40 +12860,40 @@
         <v>0.47271903292034201</v>
       </c>
       <c r="CX36" s="0">
-        <v>6.0631667600781796e-09</v>
+        <v>6.0631092008949303e-09</v>
       </c>
       <c r="CY36" s="0">
-        <v>0.24665056063701701</v>
+        <v>0.71725488786536096</v>
       </c>
       <c r="CZ36" s="0">
-        <v>2.6900041489805999</v>
+        <v>2.6900043877724502</v>
       </c>
       <c r="DA36" s="0">
-        <v>-16.880158097985301</v>
+        <v>1.7340461590806099e-08</v>
       </c>
       <c r="DB36" s="0">
-        <v>-8.7151302464656197</v>
+        <v>0.78367839346939305</v>
       </c>
       <c r="DC36" s="0">
-        <v>2.0445211989406999</v>
+        <v>2.6900053084525601</v>
       </c>
       <c r="DD36" s="0">
-        <v>-0.249999999956835</v>
+        <v>1.52445213012467e-08</v>
       </c>
       <c r="DE36" s="0">
-        <v>-3.2550764429057102</v>
+        <v>0.90837722085821104</v>
       </c>
       <c r="DF36" s="0">
-        <v>2.4205600198331099</v>
+        <v>2.6900043760194001</v>
       </c>
       <c r="DG36" s="0">
-        <v>-0.24665055457385027</v>
+        <v>-0.71725488180225172</v>
       </c>
       <c r="DH36" s="0">
-        <v>-8.1650278515196817</v>
+        <v>-0.78367837612893143</v>
       </c>
       <c r="DI36" s="0">
-        <v>3.0050764429488752</v>
+        <v>-0.90837720561368973</v>
       </c>
     </row>
     <row r="37">
@@ -13199,40 +13199,40 @@
         <v>-0.16300093884233599</v>
       </c>
       <c r="CX37" s="0">
-        <v>0.21766830096876999</v>
+        <v>0.67498033836444404</v>
       </c>
       <c r="CY37" s="0">
-        <v>0.27262319784269901</v>
+        <v>0.79054952340387097</v>
       </c>
       <c r="CZ37" s="0">
-        <v>9.7350366176944904e-08</v>
+        <v>1.84428086170535e-06</v>
       </c>
       <c r="DA37" s="0">
-        <v>0.30731970070727599</v>
+        <v>0.75156095725476502</v>
       </c>
       <c r="DB37" s="0">
-        <v>0.21032222558202501</v>
+        <v>0.74995344605549696</v>
       </c>
       <c r="DC37" s="0">
-        <v>-0.26904879709414498</v>
+        <v>4.4147073347883101e-07</v>
       </c>
       <c r="DD37" s="0">
-        <v>0.46903608727060397</v>
+        <v>0.70590963439501497</v>
       </c>
       <c r="DE37" s="0">
-        <v>0.18908745773993299</v>
+        <v>0.79727502578203102</v>
       </c>
       <c r="DF37" s="0">
-        <v>-0.342638390253862</v>
+        <v>5.4518443340044695e-07</v>
       </c>
       <c r="DG37" s="0">
-        <v>-0.054954896873929016</v>
+        <v>-0.11556918503942692</v>
       </c>
       <c r="DH37" s="0">
-        <v>0.096997475125250976</v>
+        <v>0.0016075111992680524</v>
       </c>
       <c r="DI37" s="0">
-        <v>0.27994862953067101</v>
+        <v>-0.091365391387016048</v>
       </c>
     </row>
     <row r="38">
@@ -13540,40 +13540,40 @@
         <v>0.86884175542530995</v>
       </c>
       <c r="CX38" s="0">
-        <v>1.4593856828865901e-08</v>
+        <v>1.41201531489028e-08</v>
       </c>
       <c r="CY38" s="0">
-        <v>0.25256069189702102</v>
+        <v>0.75008658534154204</v>
       </c>
       <c r="CZ38" s="0">
-        <v>18.875149951475802</v>
+        <v>18.8827761224466</v>
       </c>
       <c r="DA38" s="0">
-        <v>-24.965</v>
+        <v>2.3076808383504e-07</v>
       </c>
       <c r="DB38" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000213515402503</v>
       </c>
       <c r="DC38" s="0">
-        <v>37.108333333333299</v>
+        <v>17.3342526674836</v>
       </c>
       <c r="DD38" s="0">
-        <v>-0.24455113207891399</v>
+        <v>9.3754083165875903e-07</v>
       </c>
       <c r="DE38" s="0">
-        <v>-214.12906752292</v>
+        <v>0.85025068499525303</v>
       </c>
       <c r="DF38" s="0">
-        <v>121.357744015259</v>
+        <v>22.637130903594301</v>
       </c>
       <c r="DG38" s="0">
-        <v>-0.25256067730316417</v>
+        <v>-0.75008657122138889</v>
       </c>
       <c r="DH38" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75000190438594116</v>
       </c>
       <c r="DI38" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.85024974745442139</v>
       </c>
     </row>
     <row r="39">
@@ -13881,40 +13881,40 @@
         <v>0.757898704120893</v>
       </c>
       <c r="CX39" s="0">
-        <v>1.3883927632484999e-08</v>
+        <v>7.0997126526853399e-08</v>
       </c>
       <c r="CY39" s="0">
-        <v>0.25853861667615402</v>
+        <v>0.73963597635812905</v>
       </c>
       <c r="CZ39" s="0">
-        <v>2.0076029255281802</v>
+        <v>2.0076034369873099</v>
       </c>
       <c r="DA39" s="0">
-        <v>-0.173171548186315</v>
+        <v>2.1171675153758599e-07</v>
       </c>
       <c r="DB39" s="0">
-        <v>-0.70932847731406001</v>
+        <v>0.75318887554582004</v>
       </c>
       <c r="DC39" s="0">
-        <v>1.7618412626001501</v>
+        <v>2.0076020741938301</v>
       </c>
       <c r="DD39" s="0">
-        <v>-0.058935532263219403</v>
+        <v>2.9505692562114298e-07</v>
       </c>
       <c r="DE39" s="0">
-        <v>-0.65196508678252596</v>
+        <v>0.76606538540998903</v>
       </c>
       <c r="DF39" s="0">
-        <v>1.7736853600715301</v>
+        <v>2.0076041746056399</v>
       </c>
       <c r="DG39" s="0">
-        <v>-0.2585386027922264</v>
+        <v>-0.73963590536100254</v>
       </c>
       <c r="DH39" s="0">
-        <v>0.53615692912774504</v>
+        <v>-0.75318866382906846</v>
       </c>
       <c r="DI39" s="0">
-        <v>0.5930295545193065</v>
+        <v>-0.76606509035306336</v>
       </c>
     </row>
     <row r="40">
@@ -14222,40 +14222,40 @@
         <v>0.83533951395125905</v>
       </c>
       <c r="CX40" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY40" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ40" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA40" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB40" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC40" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD40" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE40" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF40" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG40" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH40" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI40" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="41">
@@ -14563,40 +14563,40 @@
         <v>0.55564709889817898</v>
       </c>
       <c r="CX41" s="0">
-        <v>0.49999999484403701</v>
+        <v>1.4999994580488001</v>
       </c>
       <c r="CY41" s="0">
-        <v>0.21513917379452699</v>
+        <v>0.68078192183813302</v>
       </c>
       <c r="CZ41" s="0">
-        <v>1.88824394017661</v>
+        <v>3.6602701104441802</v>
       </c>
       <c r="DA41" s="0">
-        <v>2.0000000002661502</v>
+        <v>1.4999995199610101</v>
       </c>
       <c r="DB41" s="0">
-        <v>4.41807610932418</v>
+        <v>0.92141770999747197</v>
       </c>
       <c r="DC41" s="0">
-        <v>36.945558664039098</v>
+        <v>3.7985162187569799</v>
       </c>
       <c r="DD41" s="0">
-        <v>1.99999999971391</v>
+        <v>1.4999999168407201</v>
       </c>
       <c r="DE41" s="0">
-        <v>-60.487436804044798</v>
+        <v>0.66140035155023602</v>
       </c>
       <c r="DF41" s="0">
-        <v>114.957523325571</v>
+        <v>9.1673656381956299</v>
       </c>
       <c r="DG41" s="0">
-        <v>0.28486082104951005</v>
+        <v>0.81921753621066706</v>
       </c>
       <c r="DH41" s="0">
-        <v>-2.4180761090580298</v>
+        <v>0.57858180996353814</v>
       </c>
       <c r="DI41" s="0">
-        <v>62.487436803758705</v>
+        <v>0.83859956529048407</v>
       </c>
     </row>
     <row r="42">
@@ -14904,40 +14904,40 @@
         <v>0.73679027501203798</v>
       </c>
       <c r="CX42" s="0">
-        <v>0.00065886594430574603</v>
+        <v>0.00065874846259499499</v>
       </c>
       <c r="CY42" s="0">
-        <v>0.249744288632259</v>
+        <v>0.73643406294253799</v>
       </c>
       <c r="CZ42" s="0">
-        <v>2.1973261593236302</v>
+        <v>2.19732566181596</v>
       </c>
       <c r="DA42" s="0">
-        <v>-0.040857701650013803</v>
+        <v>1.50644183583849e-07</v>
       </c>
       <c r="DB42" s="0">
-        <v>-1.0849599778504999</v>
+        <v>0.74173111650732004</v>
       </c>
       <c r="DC42" s="0">
-        <v>2.1098539172174902</v>
+        <v>2.19282426438506</v>
       </c>
       <c r="DD42" s="0">
-        <v>0.0040625406626174599</v>
+        <v>0.0040635493488721504</v>
       </c>
       <c r="DE42" s="0">
-        <v>-1.5774627626156501</v>
+        <v>0.717888259239857</v>
       </c>
       <c r="DF42" s="0">
-        <v>2.2134376161511899</v>
+        <v>2.2134131032059301</v>
       </c>
       <c r="DG42" s="0">
-        <v>-0.24908542268795325</v>
+        <v>-0.73577531447994304</v>
       </c>
       <c r="DH42" s="0">
-        <v>1.0441022762004861</v>
+        <v>-0.74173096586313647</v>
       </c>
       <c r="DI42" s="0">
-        <v>1.5815253032782675</v>
+        <v>-0.7138247098909849</v>
       </c>
     </row>
     <row r="43">
@@ -15245,40 +15245,40 @@
         <v>0.64934891946828599</v>
       </c>
       <c r="CX43" s="0">
-        <v>2.1924229993415699e-09</v>
+        <v>2.1923921629314398e-09</v>
       </c>
       <c r="CY43" s="0">
-        <v>0.252196944751295</v>
+        <v>0.74457310132375598</v>
       </c>
       <c r="CZ43" s="0">
-        <v>2.1815823797786398</v>
+        <v>2.1815823425549099</v>
       </c>
       <c r="DA43" s="0">
-        <v>-0.20408300534295601</v>
+        <v>1.4686666124985201e-07</v>
       </c>
       <c r="DB43" s="0">
-        <v>-0.30869412729456902</v>
+        <v>0.74185080786776503</v>
       </c>
       <c r="DC43" s="0">
-        <v>1.89534212443462</v>
+        <v>2.1815827145594202</v>
       </c>
       <c r="DD43" s="0">
-        <v>-0.053255886896813598</v>
+        <v>1.9513352398455999e-07</v>
       </c>
       <c r="DE43" s="0">
-        <v>-1.8114099261377099</v>
+        <v>0.74350142541931996</v>
       </c>
       <c r="DF43" s="0">
-        <v>1.97522645895351</v>
+        <v>2.1815832435782299</v>
       </c>
       <c r="DG43" s="0">
-        <v>-0.25219694255887198</v>
+        <v>-0.74457309913136382</v>
       </c>
       <c r="DH43" s="0">
-        <v>0.10461112195161301</v>
+        <v>-0.74185066100110375</v>
       </c>
       <c r="DI43" s="0">
-        <v>1.7581540392408963</v>
+        <v>-0.74350123028579596</v>
       </c>
     </row>
     <row r="44">
@@ -15586,40 +15586,40 @@
         <v>0.64757603549773002</v>
       </c>
       <c r="CX44" s="0">
-        <v>0.062816779811488296</v>
+        <v>0.062816791082920903</v>
       </c>
       <c r="CY44" s="0">
-        <v>0.250044722525741</v>
+        <v>0.74856701827027605</v>
       </c>
       <c r="CZ44" s="0">
-        <v>1.27583533696715</v>
+        <v>1.27583538939033</v>
       </c>
       <c r="DA44" s="0">
-        <v>0.24360365592255401</v>
+        <v>0.24360546050812601</v>
       </c>
       <c r="DB44" s="0">
-        <v>0.43653437916870103</v>
+        <v>0.75219254934450896</v>
       </c>
       <c r="DC44" s="0">
-        <v>1.35453354430766</v>
+        <v>1.3545046742843601</v>
       </c>
       <c r="DD44" s="0">
-        <v>0.32403275292755201</v>
+        <v>0.32404184679391501</v>
       </c>
       <c r="DE44" s="0">
-        <v>0.83452968936519401</v>
+        <v>0.77976324718018997</v>
       </c>
       <c r="DF44" s="0">
-        <v>1.90615615925478</v>
+        <v>1.90618210844761</v>
       </c>
       <c r="DG44" s="0">
-        <v>-0.18722794271425269</v>
+        <v>-0.68575022718735512</v>
       </c>
       <c r="DH44" s="0">
-        <v>-0.19293072324614702</v>
+        <v>-0.50858708883638293</v>
       </c>
       <c r="DI44" s="0">
-        <v>-0.51049693643764193</v>
+        <v>-0.45572140038627496</v>
       </c>
     </row>
     <row r="45">
@@ -15927,40 +15927,40 @@
         <v>0.75931697529305697</v>
       </c>
       <c r="CX45" s="0">
-        <v>0.23347139232241301</v>
+        <v>0.23347139210242099</v>
       </c>
       <c r="CY45" s="0">
-        <v>0.24979741815564899</v>
+        <v>0.70096649006096901</v>
       </c>
       <c r="CZ45" s="0">
-        <v>1.3255619439903701</v>
+        <v>1.3255619639726699</v>
       </c>
       <c r="DA45" s="0">
-        <v>0.68756061928488599</v>
+        <v>0.687563415128563</v>
       </c>
       <c r="DB45" s="0">
-        <v>-0.50930904852803305</v>
+        <v>0.75459806945653896</v>
       </c>
       <c r="DC45" s="0">
-        <v>1.5448337558112499</v>
+        <v>1.5448316549798999</v>
       </c>
       <c r="DD45" s="0">
-        <v>0.84124010722587805</v>
+        <v>0.84123816816752395</v>
       </c>
       <c r="DE45" s="0">
-        <v>-0.971756242104174</v>
+        <v>0.77898790845699495</v>
       </c>
       <c r="DF45" s="0">
-        <v>3.0273050083522901</v>
+        <v>3.0272875457922499</v>
       </c>
       <c r="DG45" s="0">
-        <v>-0.016326025833235974</v>
+        <v>-0.46749509795854804</v>
       </c>
       <c r="DH45" s="0">
-        <v>1.1968696678129191</v>
+        <v>-0.067034654327975951</v>
       </c>
       <c r="DI45" s="0">
-        <v>1.812996349330052</v>
+        <v>0.062250259710528999</v>
       </c>
     </row>
     <row r="46">
@@ -16268,40 +16268,40 @@
         <v>0.83533951395125905</v>
       </c>
       <c r="CX46" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY46" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ46" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA46" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB46" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC46" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD46" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE46" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF46" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG46" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH46" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI46" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="47">
@@ -16609,40 +16609,40 @@
         <v>0.59402789037633397</v>
       </c>
       <c r="CX47" s="0">
-        <v>2.55104670247109e-09</v>
+        <v>1.5703105701881801e-06</v>
       </c>
       <c r="CY47" s="0">
-        <v>0.13910098625464201</v>
+        <v>0.75008318953489705</v>
       </c>
       <c r="CZ47" s="0">
-        <v>20.901813460934601</v>
+        <v>16.952900810569801</v>
       </c>
       <c r="DA47" s="0">
-        <v>-0.0048428917226100996</v>
+        <v>2.8767867930187203e-07</v>
       </c>
       <c r="DB47" s="0">
-        <v>-0.56824283001869302</v>
+        <v>0.75001421822918002</v>
       </c>
       <c r="DC47" s="0">
-        <v>29.3160181808766</v>
+        <v>18.536323705171402</v>
       </c>
       <c r="DD47" s="0">
-        <v>-0.00019853257000296799</v>
+        <v>5.8869699401711599e-08</v>
       </c>
       <c r="DE47" s="0">
-        <v>-683.60970260258796</v>
+        <v>0.29222811361011902</v>
       </c>
       <c r="DF47" s="0">
-        <v>710.00019576748298</v>
+        <v>18.1210834032062</v>
       </c>
       <c r="DG47" s="0">
-        <v>-0.1391009837035953</v>
+        <v>-0.75008161922432681</v>
       </c>
       <c r="DH47" s="0">
-        <v>0.56339993829608292</v>
+        <v>-0.7500139305505007</v>
       </c>
       <c r="DI47" s="0">
-        <v>683.60950407001792</v>
+        <v>-0.29222805474041963</v>
       </c>
     </row>
     <row r="48">
@@ -16950,40 +16950,40 @@
         <v>0.44742160295607902</v>
       </c>
       <c r="CX48" s="0">
-        <v>0.499999616729845</v>
+        <v>0.80493368223160899</v>
       </c>
       <c r="CY48" s="0">
-        <v>0.25080458032009301</v>
+        <v>0.69409761271308501</v>
       </c>
       <c r="CZ48" s="0">
-        <v>0.91206842942787902</v>
+        <v>0.752325521418438</v>
       </c>
       <c r="DA48" s="0">
-        <v>1.57541351042808</v>
+        <v>1.4999996485944</v>
       </c>
       <c r="DB48" s="0">
-        <v>-1.0009082093094801</v>
+        <v>0.74990497705140702</v>
       </c>
       <c r="DC48" s="0">
-        <v>0.785602491659524</v>
+        <v>0.817525920103362</v>
       </c>
       <c r="DD48" s="0">
-        <v>2.7936760026051202</v>
+        <v>1.4999993272579799</v>
       </c>
       <c r="DE48" s="0">
-        <v>-3.3014208401721601</v>
+        <v>0.75182536121181498</v>
       </c>
       <c r="DF48" s="0">
-        <v>1.1560462251291099</v>
+        <v>1.2129607595590399</v>
       </c>
       <c r="DG48" s="0">
-        <v>0.24919503640975199</v>
+        <v>0.11083606951852398</v>
       </c>
       <c r="DH48" s="0">
-        <v>2.5763217197375603</v>
+        <v>0.75009467154299303</v>
       </c>
       <c r="DI48" s="0">
-        <v>6.0950968427772807</v>
+        <v>0.74817396604616493</v>
       </c>
     </row>
     <row r="49">
@@ -17291,40 +17291,40 @@
         <v>0.53910873637300205</v>
       </c>
       <c r="CX49" s="0">
-        <v>4.5661683137799102e-08</v>
+        <v>9.1331078349163006e-09</v>
       </c>
       <c r="CY49" s="0">
-        <v>0.25114724414165601</v>
+        <v>0.70855139566994796</v>
       </c>
       <c r="CZ49" s="0">
-        <v>1.58740111959999</v>
+        <v>1.58740104587069</v>
       </c>
       <c r="DA49" s="0">
-        <v>-0.39769634689118999</v>
+        <v>1.5369567424718299e-07</v>
       </c>
       <c r="DB49" s="0">
-        <v>-0.48922523514572502</v>
+        <v>0.65439405321904598</v>
       </c>
       <c r="DC49" s="0">
-        <v>1.2682830671549099</v>
+        <v>1.5874010410073001</v>
       </c>
       <c r="DD49" s="0">
-        <v>-0.079610924009866704</v>
+        <v>2.4241241155288098e-07</v>
       </c>
       <c r="DE49" s="0">
-        <v>-0.75350556591469897</v>
+        <v>0.63102310684166296</v>
       </c>
       <c r="DF49" s="0">
-        <v>1.34523391499788</v>
+        <v>1.5874013751807401</v>
       </c>
       <c r="DG49" s="0">
-        <v>-0.25114719847997286</v>
+        <v>-0.70855138653684013</v>
       </c>
       <c r="DH49" s="0">
-        <v>0.091528888254535035</v>
+        <v>-0.65439389952337168</v>
       </c>
       <c r="DI49" s="0">
-        <v>0.67389464190483228</v>
+        <v>-0.63102286442925137</v>
       </c>
     </row>
     <row r="50">
@@ -17632,40 +17632,40 @@
         <v>0.87017645562451196</v>
       </c>
       <c r="CX50" s="0">
-        <v>1.7436398607017301e-10</v>
+        <v>1.41967979653206e-08</v>
       </c>
       <c r="CY50" s="0">
-        <v>0.418786867086828</v>
+        <v>0.74981860910365805</v>
       </c>
       <c r="CZ50" s="0">
-        <v>15.2613445413979</v>
+        <v>18.798628304133999</v>
       </c>
       <c r="DA50" s="0">
-        <v>-24.965</v>
+        <v>4.2340172195802302e-08</v>
       </c>
       <c r="DB50" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.887974158783564</v>
       </c>
       <c r="DC50" s="0">
-        <v>37.108333333333299</v>
+        <v>18.890351819190599</v>
       </c>
       <c r="DD50" s="0">
-        <v>-0.22857891151241</v>
+        <v>5.1956518724761503e-08</v>
       </c>
       <c r="DE50" s="0">
-        <v>-279.209154384496</v>
+        <v>1.28714309875236</v>
       </c>
       <c r="DF50" s="0">
-        <v>158.13435605280799</v>
+        <v>15.364054731767499</v>
       </c>
       <c r="DG50" s="0">
-        <v>-0.41878686691246403</v>
+        <v>-0.74981859490686009</v>
       </c>
       <c r="DH50" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.88797411644339186</v>
       </c>
       <c r="DI50" s="0">
-        <v>278.98057547298362</v>
+        <v>-1.2871430467958414</v>
       </c>
     </row>
     <row r="51">
@@ -17973,40 +17973,40 @@
         <v>0.68342524946957095</v>
       </c>
       <c r="CX51" s="0">
-        <v>0.49999988544325202</v>
+        <v>0.67033021327532405</v>
       </c>
       <c r="CY51" s="0">
-        <v>0.25043253032064999</v>
+        <v>0.69346076306607796</v>
       </c>
       <c r="CZ51" s="0">
-        <v>0.91206846130346797</v>
+        <v>0.79803315134617503</v>
       </c>
       <c r="DA51" s="0">
-        <v>1.5664102485337399</v>
+        <v>1.4999999457300801</v>
       </c>
       <c r="DB51" s="0">
-        <v>-1.68820745485065</v>
+        <v>0.75112645710563497</v>
       </c>
       <c r="DC51" s="0">
-        <v>1.1344961309385999</v>
+        <v>1.1683103160057</v>
       </c>
       <c r="DD51" s="0">
-        <v>5.5240718517880403</v>
+        <v>1.4999999945714</v>
       </c>
       <c r="DE51" s="0">
-        <v>-5.9219631857968702</v>
+        <v>1.14810669666384</v>
       </c>
       <c r="DF51" s="0">
-        <v>3.2063665824905399</v>
+        <v>3.8851633233701799</v>
       </c>
       <c r="DG51" s="0">
-        <v>0.24956735512260203</v>
+        <v>-0.023130549790753907</v>
       </c>
       <c r="DH51" s="0">
-        <v>3.2546177033843899</v>
+        <v>0.74887348862444514</v>
       </c>
       <c r="DI51" s="0">
-        <v>11.44603503758491</v>
+        <v>0.35189329790755997</v>
       </c>
     </row>
     <row r="52">
@@ -18314,40 +18314,40 @@
         <v>0.65597291554095905</v>
       </c>
       <c r="CX52" s="0">
-        <v>0.111422818839905</v>
+        <v>0.11142282272826</v>
       </c>
       <c r="CY52" s="0">
-        <v>0.25005395406703501</v>
+        <v>0.74998653131275395</v>
       </c>
       <c r="CZ52" s="0">
-        <v>1.2796223047851201</v>
+        <v>1.2796222755023099</v>
       </c>
       <c r="DA52" s="0">
-        <v>0.41660300694575803</v>
+        <v>0.416590494599691</v>
       </c>
       <c r="DB52" s="0">
-        <v>-0.50492029490622203</v>
+        <v>0.73483392930468605</v>
       </c>
       <c r="DC52" s="0">
-        <v>1.4269756851733899</v>
+        <v>1.4269433060196299</v>
       </c>
       <c r="DD52" s="0">
-        <v>0.55554845002806097</v>
+        <v>0.55554381777501805</v>
       </c>
       <c r="DE52" s="0">
-        <v>-0.93964462655774506</v>
+        <v>0.79324665538176597</v>
       </c>
       <c r="DF52" s="0">
-        <v>2.4306108478272899</v>
+        <v>2.4305910808469098</v>
       </c>
       <c r="DG52" s="0">
-        <v>-0.13863113522713</v>
+        <v>-0.63856370858449396</v>
       </c>
       <c r="DH52" s="0">
-        <v>0.92152330185198006</v>
+        <v>-0.31824343470499505</v>
       </c>
       <c r="DI52" s="0">
-        <v>1.4951930765858061</v>
+        <v>-0.23770283760674793</v>
       </c>
     </row>
     <row r="53">
@@ -18655,40 +18655,40 @@
         <v>0.91936246321511705</v>
       </c>
       <c r="CX53" s="0">
-        <v>0.27749867866904498</v>
+        <v>0.27749868325399302</v>
       </c>
       <c r="CY53" s="0">
-        <v>0.24688294417830201</v>
+        <v>0.74701002871808897</v>
       </c>
       <c r="CZ53" s="0">
-        <v>0.47075230728738998</v>
+        <v>0.47075232853201199</v>
       </c>
       <c r="DA53" s="0">
-        <v>0.96196176835065195</v>
+        <v>0.96197662575696996</v>
       </c>
       <c r="DB53" s="0">
-        <v>-0.68343016468571405</v>
+        <v>0.75282394742595204</v>
       </c>
       <c r="DC53" s="0">
-        <v>0.67487863276476301</v>
+        <v>0.67486622335903601</v>
       </c>
       <c r="DD53" s="0">
-        <v>144.00013103381701</v>
+        <v>1.49999998940753</v>
       </c>
       <c r="DE53" s="0">
-        <v>-67.985220203165497</v>
+        <v>0.76835256407672003</v>
       </c>
       <c r="DF53" s="0">
-        <v>1.77001360677042</v>
+        <v>2.16520169165232</v>
       </c>
       <c r="DG53" s="0">
-        <v>0.03061573449074298</v>
+        <v>-0.46951134546409595</v>
       </c>
       <c r="DH53" s="0">
-        <v>1.645391933036366</v>
+        <v>0.20915267833101792</v>
       </c>
       <c r="DI53" s="0">
-        <v>211.98535123698252</v>
+        <v>0.73164742533080995</v>
       </c>
     </row>
     <row r="54">
@@ -18996,40 +18996,40 @@
         <v>0.92515120277644203</v>
       </c>
       <c r="CX54" s="0">
-        <v>6.5712161790289399e-09</v>
+        <v>6.5712196451856999e-09</v>
       </c>
       <c r="CY54" s="0">
-        <v>0.25125204448935401</v>
+        <v>0.72925433013010998</v>
       </c>
       <c r="CZ54" s="0">
-        <v>2.1928248190375101</v>
+        <v>2.1928236191784198</v>
       </c>
       <c r="DA54" s="0">
-        <v>-0.41167468703279098</v>
+        <v>9.8559388999504894e-08</v>
       </c>
       <c r="DB54" s="0">
-        <v>-0.43287507244683998</v>
+        <v>0.73888079570849097</v>
       </c>
       <c r="DC54" s="0">
-        <v>1.77031851483276</v>
+        <v>2.1928240035670901</v>
       </c>
       <c r="DD54" s="0">
-        <v>-0.080295736990482799</v>
+        <v>3.1703112789170001e-08</v>
       </c>
       <c r="DE54" s="0">
-        <v>-0.16734924327504599</v>
+        <v>0.74329584687681605</v>
       </c>
       <c r="DF54" s="0">
-        <v>1.88448459539195</v>
+        <v>2.1928237695956398</v>
       </c>
       <c r="DG54" s="0">
-        <v>-0.25125203791813783</v>
+        <v>-0.72925432355889031</v>
       </c>
       <c r="DH54" s="0">
-        <v>0.021200385414049006</v>
+        <v>-0.73888069714910198</v>
       </c>
       <c r="DI54" s="0">
-        <v>0.087053506284563195</v>
+        <v>-0.74329581517370324</v>
       </c>
     </row>
     <row r="55">
@@ -19337,40 +19337,40 @@
         <v>0.86748390473319503</v>
       </c>
       <c r="CX55" s="0">
-        <v>1.41739368191465e-08</v>
+        <v>1.41149552700507e-08</v>
       </c>
       <c r="CY55" s="0">
-        <v>0.24998744256379399</v>
+        <v>0.75003614405224495</v>
       </c>
       <c r="CZ55" s="0">
-        <v>18.775772519524299</v>
+        <v>18.889711168296401</v>
       </c>
       <c r="DA55" s="0">
-        <v>-24.965</v>
+        <v>4.2510970030221202e-08</v>
       </c>
       <c r="DB55" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74998764926750505</v>
       </c>
       <c r="DC55" s="0">
-        <v>37.108333333333299</v>
+        <v>18.808586689695399</v>
       </c>
       <c r="DD55" s="0">
-        <v>-0.24455113207891399</v>
+        <v>4.24390792960197e-08</v>
       </c>
       <c r="DE55" s="0">
-        <v>-214.12906752292</v>
+        <v>0.74999998863444095</v>
       </c>
       <c r="DF55" s="0">
-        <v>121.357744015259</v>
+        <v>18.8510052383789</v>
       </c>
       <c r="DG55" s="0">
-        <v>-0.24998742838985716</v>
+        <v>-0.75003612993728963</v>
       </c>
       <c r="DH55" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74998760675653497</v>
       </c>
       <c r="DI55" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.7499999461953617</v>
       </c>
     </row>
     <row r="56">
@@ -19678,40 +19678,40 @@
         <v>0.666436593127819</v>
       </c>
       <c r="CX56" s="0">
-        <v>0.047351838266211102</v>
+        <v>0.047351838881656103</v>
       </c>
       <c r="CY56" s="0">
-        <v>0.25052163551846701</v>
+        <v>0.75538372358657302</v>
       </c>
       <c r="CZ56" s="0">
-        <v>1.5747599416931299</v>
+        <v>1.57475992232188</v>
       </c>
       <c r="DA56" s="0">
-        <v>0.100096669051536</v>
+        <v>0.100086152831623</v>
       </c>
       <c r="DB56" s="0">
-        <v>-0.38328660212526899</v>
+        <v>0.74531719754944703</v>
       </c>
       <c r="DC56" s="0">
-        <v>1.48724040183707</v>
+        <v>1.4872544327841899</v>
       </c>
       <c r="DD56" s="0">
-        <v>0.13190347901652899</v>
+        <v>0.131903251197556</v>
       </c>
       <c r="DE56" s="0">
-        <v>2.9684974015517298</v>
+        <v>0.770545233235719</v>
       </c>
       <c r="DF56" s="0">
-        <v>1.8236349083603201</v>
+        <v>1.8236140430582499</v>
       </c>
       <c r="DG56" s="0">
-        <v>-0.20316979725225592</v>
+        <v>-0.70803188470491696</v>
       </c>
       <c r="DH56" s="0">
-        <v>0.48338327117680502</v>
+        <v>-0.645231044717824</v>
       </c>
       <c r="DI56" s="0">
-        <v>-2.8365939225352008</v>
+        <v>-0.63864198203816303</v>
       </c>
     </row>
     <row r="57">
@@ -20019,40 +20019,40 @@
         <v>0.98285898165574903</v>
       </c>
       <c r="CX57" s="0">
-        <v>1.3731312575772e-07</v>
+        <v>1.3731320601088801e-07</v>
       </c>
       <c r="CY57" s="0">
-        <v>0.25041866286487402</v>
+        <v>0.69586069763862202</v>
       </c>
       <c r="CZ57" s="0">
-        <v>1.8042301680033499</v>
+        <v>1.80423026091196</v>
       </c>
       <c r="DA57" s="0">
-        <v>-0.069285949627791596</v>
+        <v>1.01225471350442e-07</v>
       </c>
       <c r="DB57" s="0">
-        <v>-0.246026481164552</v>
+        <v>0.68388894251642096</v>
       </c>
       <c r="DC57" s="0">
-        <v>1.7025156539667701</v>
+        <v>1.80422968756264</v>
       </c>
       <c r="DD57" s="0">
-        <v>0.028724151668438599</v>
+        <v>0.028720793125492299</v>
       </c>
       <c r="DE57" s="0">
-        <v>-0.81058210003652797</v>
+        <v>0.72229991776816505</v>
       </c>
       <c r="DF57" s="0">
-        <v>1.9225932242199499</v>
+        <v>1.9225942810266501</v>
       </c>
       <c r="DG57" s="0">
-        <v>-0.25041852555174826</v>
+        <v>-0.69586056032541599</v>
       </c>
       <c r="DH57" s="0">
-        <v>0.17674053153676039</v>
+        <v>-0.68388884129094962</v>
       </c>
       <c r="DI57" s="0">
-        <v>0.83930625170496653</v>
+        <v>-0.6935791246426728</v>
       </c>
     </row>
     <row r="58">
@@ -20360,40 +20360,40 @@
         <v>0.87092074870949998</v>
       </c>
       <c r="CX58" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY58" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ58" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA58" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB58" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC58" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD58" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE58" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF58" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG58" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH58" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI58" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="59">
@@ -20701,40 +20701,40 @@
         <v>-0.12649370943694499</v>
       </c>
       <c r="CX59" s="0">
-        <v>0.022272435042664698</v>
+        <v>0.022272447249776998</v>
       </c>
       <c r="CY59" s="0">
-        <v>0.24754226613128799</v>
+        <v>0.774580847114125</v>
       </c>
       <c r="CZ59" s="0">
-        <v>0.213064989131104</v>
+        <v>0.21306498299607601</v>
       </c>
       <c r="DA59" s="0">
-        <v>0.00060558850825475198</v>
+        <v>0.00068777487782363501</v>
       </c>
       <c r="DB59" s="0">
-        <v>0.062291894579093003</v>
+        <v>0.715324402641763</v>
       </c>
       <c r="DC59" s="0">
-        <v>0.20240107277573199</v>
+        <v>0.20241485323254299</v>
       </c>
       <c r="DD59" s="0">
-        <v>-0.026657154842520101</v>
+        <v>1.98509372212514e-06</v>
       </c>
       <c r="DE59" s="0">
-        <v>-0.0140795586084277</v>
+        <v>0.74998964394761203</v>
       </c>
       <c r="DF59" s="0">
-        <v>0.19142141282921801</v>
+        <v>0.20231074610649399</v>
       </c>
       <c r="DG59" s="0">
-        <v>-0.22526983108862331</v>
+        <v>-0.75230839986434805</v>
       </c>
       <c r="DH59" s="0">
-        <v>-0.061686306070838248</v>
+        <v>-0.71463662776393932</v>
       </c>
       <c r="DI59" s="0">
-        <v>-0.012577596234092402</v>
+        <v>-0.74998765885388985</v>
       </c>
     </row>
     <row r="60">
@@ -21042,40 +21042,40 @@
         <v>0.83172265126445599</v>
       </c>
       <c r="CX60" s="0">
-        <v>1.86848480969332e-10</v>
+        <v>1.8246504095337001e-08</v>
       </c>
       <c r="CY60" s="0">
-        <v>0.42029594553209698</v>
+        <v>0.68367731563506795</v>
       </c>
       <c r="CZ60" s="0">
-        <v>15.2591278309262</v>
+        <v>19.789943389498301</v>
       </c>
       <c r="DA60" s="0">
-        <v>-24.965</v>
+        <v>4.6949608973222798e-08</v>
       </c>
       <c r="DB60" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75002417069687</v>
       </c>
       <c r="DC60" s="0">
-        <v>37.108333333333299</v>
+        <v>18.888182670893599</v>
       </c>
       <c r="DD60" s="0">
-        <v>-0.19545403511568099</v>
+        <v>1.87241705533176e-07</v>
       </c>
       <c r="DE60" s="0">
-        <v>-291.74500933229598</v>
+        <v>0.97522913156153501</v>
       </c>
       <c r="DF60" s="0">
-        <v>165.09901953444501</v>
+        <v>27.710842839678801</v>
       </c>
       <c r="DG60" s="0">
-        <v>-0.4202959453452485</v>
+        <v>-0.68367729738856386</v>
       </c>
       <c r="DH60" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75002412374726102</v>
       </c>
       <c r="DI60" s="0">
-        <v>291.54955529718029</v>
+        <v>-0.97522894431982943</v>
       </c>
     </row>
     <row r="61">
@@ -21383,40 +21383,40 @@
         <v>0.82873865139403102</v>
       </c>
       <c r="CX61" s="0">
-        <v>4.0184280434542301e-07</v>
+        <v>1.11358390667128e-07</v>
       </c>
       <c r="CY61" s="0">
-        <v>0.30788381411384702</v>
+        <v>0.74998640352046397</v>
       </c>
       <c r="CZ61" s="0">
-        <v>19.429854952625298</v>
+        <v>17.104912966511801</v>
       </c>
       <c r="DA61" s="0">
-        <v>-24.965</v>
+        <v>6.1523382621968296e-08</v>
       </c>
       <c r="DB61" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.76159401336976096</v>
       </c>
       <c r="DC61" s="0">
-        <v>37.108333333333299</v>
+        <v>18.5717694082152</v>
       </c>
       <c r="DD61" s="0">
-        <v>-0.234925425378054</v>
+        <v>2.0996746849113299e-07</v>
       </c>
       <c r="DE61" s="0">
-        <v>-233.57995393932899</v>
+        <v>0.94044824727662102</v>
       </c>
       <c r="DF61" s="0">
-        <v>132.31774306443799</v>
+        <v>30.627460325432299</v>
       </c>
       <c r="DG61" s="0">
-        <v>-0.30788341227104266</v>
+        <v>-0.74998629216207335</v>
       </c>
       <c r="DH61" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.76159395184637835</v>
       </c>
       <c r="DI61" s="0">
-        <v>233.34502851395092</v>
+        <v>-0.9404480373091525</v>
       </c>
     </row>
     <row r="62">
@@ -21724,40 +21724,40 @@
         <v>0.68044547709427405</v>
       </c>
       <c r="CX62" s="0">
-        <v>2.6740882687472702e-07</v>
+        <v>4.9034607737004703e-08</v>
       </c>
       <c r="CY62" s="0">
-        <v>0.25160860592742501</v>
+        <v>0.69358670499198005</v>
       </c>
       <c r="CZ62" s="0">
-        <v>1.04804902570128</v>
+        <v>1.0480480122246401</v>
       </c>
       <c r="DA62" s="0">
-        <v>-0.015527892881608499</v>
+        <v>1.1421410069498999e-06</v>
       </c>
       <c r="DB62" s="0">
-        <v>-0.13687584592101101</v>
+        <v>0.67636000713045097</v>
       </c>
       <c r="DC62" s="0">
-        <v>1.0348532383579101</v>
+        <v>1.04804901222934</v>
       </c>
       <c r="DD62" s="0">
-        <v>0.157882302720181</v>
+        <v>0.15787659551680999</v>
       </c>
       <c r="DE62" s="0">
-        <v>-2.3907171937470801</v>
+        <v>0.73383476049072605</v>
       </c>
       <c r="DF62" s="0">
-        <v>1.3840783298075101</v>
+        <v>1.38406974125011</v>
       </c>
       <c r="DG62" s="0">
-        <v>-0.25160833851859815</v>
+        <v>-0.69358665595737234</v>
       </c>
       <c r="DH62" s="0">
-        <v>0.12134795303940252</v>
+        <v>-0.67635886498944398</v>
       </c>
       <c r="DI62" s="0">
-        <v>2.5485994964672614</v>
+        <v>-0.57595816497391605</v>
       </c>
     </row>
     <row r="63">
@@ -22065,40 +22065,40 @@
         <v>0.55701188402372503</v>
       </c>
       <c r="CX63" s="0">
-        <v>5.9339022080266701e-09</v>
+        <v>5.9342237000073898e-09</v>
       </c>
       <c r="CY63" s="0">
-        <v>0.25397135945107102</v>
+        <v>0.72295359519024005</v>
       </c>
       <c r="CZ63" s="0">
-        <v>2.77172795140965</v>
+        <v>2.7717278535941001</v>
       </c>
       <c r="DA63" s="0">
-        <v>-15.322219692720701</v>
+        <v>8.4731269378366801e-08</v>
       </c>
       <c r="DB63" s="0">
-        <v>33.195583595497197</v>
+        <v>0.834619321886645</v>
       </c>
       <c r="DC63" s="0">
-        <v>2.19282363464538</v>
+        <v>2.7717279842673301</v>
       </c>
       <c r="DD63" s="0">
-        <v>-0.24999998959500799</v>
+        <v>1.5023303247752299e-08</v>
       </c>
       <c r="DE63" s="0">
-        <v>-3.44185730824156</v>
+        <v>0.85671851043731595</v>
       </c>
       <c r="DF63" s="0">
-        <v>2.5250679669384199</v>
+        <v>2.7717279330561002</v>
       </c>
       <c r="DG63" s="0">
-        <v>-0.25397135351716882</v>
+        <v>-0.72295358925601638</v>
       </c>
       <c r="DH63" s="0">
-        <v>-48.517803288217898</v>
+        <v>-0.83461923715537567</v>
       </c>
       <c r="DI63" s="0">
-        <v>3.191857318646552</v>
+        <v>-0.85671849541401268</v>
       </c>
     </row>
     <row r="64">
@@ -22404,40 +22404,40 @@
         <v>0.82851051827688504</v>
       </c>
       <c r="CX64" s="0">
-        <v>7.5626068428279003e-10</v>
+        <v>9.0933417994810406e-08</v>
       </c>
       <c r="CY64" s="0">
-        <v>0.25042821010127297</v>
+        <v>0.74999598273385504</v>
       </c>
       <c r="CZ64" s="0">
-        <v>20.763211211034999</v>
+        <v>17.250717206800399</v>
       </c>
       <c r="DA64" s="0">
-        <v>-24.965</v>
+        <v>4.2451061110772299e-10</v>
       </c>
       <c r="DB64" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.653560312969933</v>
       </c>
       <c r="DC64" s="0">
-        <v>37.108333333333299</v>
+        <v>22.123659476982301</v>
       </c>
       <c r="DD64" s="0">
-        <v>-0.248671771390156</v>
+        <v>5.0111797347520999e-08</v>
       </c>
       <c r="DE64" s="0">
-        <v>-195.059051746259</v>
+        <v>0.74999229122078603</v>
       </c>
       <c r="DF64" s="0">
-        <v>110.63724739046</v>
+        <v>18.7825162806759</v>
       </c>
       <c r="DG64" s="0">
-        <v>-0.25042820934501231</v>
+        <v>-0.74999589180043702</v>
       </c>
       <c r="DH64" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.65356031254542235</v>
       </c>
       <c r="DI64" s="0">
-        <v>194.81037997486885</v>
+        <v>-0.74999224110898866</v>
       </c>
     </row>
     <row r="65">
@@ -22745,40 +22745,40 @@
         <v>0.82929531749113405</v>
       </c>
       <c r="CX65" s="0">
-        <v>0.30033126278669597</v>
+        <v>0.30033128322245101</v>
       </c>
       <c r="CY65" s="0">
-        <v>0.24982651187220201</v>
+        <v>0.75224335930495201</v>
       </c>
       <c r="CZ65" s="0">
-        <v>0.96352607628668696</v>
+        <v>0.96352603050489405</v>
       </c>
       <c r="DA65" s="0">
-        <v>0.88962788694714301</v>
+        <v>0.88961317555189501</v>
       </c>
       <c r="DB65" s="0">
-        <v>-0.36324741576298603</v>
+        <v>0.75003088062321399</v>
       </c>
       <c r="DC65" s="0">
-        <v>1.0911773622776799</v>
+        <v>1.0912087738290199</v>
       </c>
       <c r="DD65" s="0">
-        <v>2.4949989809587301</v>
+        <v>1.49999997108</v>
       </c>
       <c r="DE65" s="0">
-        <v>-1.0961083004600001</v>
+        <v>0.74824735299368805</v>
       </c>
       <c r="DF65" s="0">
-        <v>2.1743060267158998</v>
+        <v>2.3818550226108202</v>
       </c>
       <c r="DG65" s="0">
-        <v>0.050504750914493968</v>
+        <v>-0.451912076082501</v>
       </c>
       <c r="DH65" s="0">
-        <v>1.2528753027101289</v>
+        <v>0.13958229492868102</v>
       </c>
       <c r="DI65" s="0">
-        <v>3.5911072814187301</v>
+        <v>0.751752618086312</v>
       </c>
     </row>
     <row r="66">
@@ -23086,40 +23086,40 @@
         <v>0.24373516549060101</v>
       </c>
       <c r="CX66" s="0">
-        <v>1.61759052620606e-08</v>
+        <v>1.6180053499151302e-08</v>
       </c>
       <c r="CY66" s="0">
-        <v>0.25225345258930398</v>
+        <v>0.67550900474897202</v>
       </c>
       <c r="CZ66" s="0">
-        <v>1.34621402414943</v>
+        <v>1.3462139255441801</v>
       </c>
       <c r="DA66" s="0">
-        <v>-0.25289442927512201</v>
+        <v>2.5259761693550502e-07</v>
       </c>
       <c r="DB66" s="0">
-        <v>-0.58594842805313196</v>
+        <v>0.65465775059924902</v>
       </c>
       <c r="DC66" s="0">
-        <v>1.13849948648249</v>
+        <v>1.3462143360836201</v>
       </c>
       <c r="DD66" s="0">
-        <v>-0.121786691142394</v>
+        <v>7.2540935355011496e-08</v>
       </c>
       <c r="DE66" s="0">
-        <v>-0.30000018620251701</v>
+        <v>0.62531533565104902</v>
       </c>
       <c r="DF66" s="0">
-        <v>1.06019948930807</v>
+        <v>1.34621398159225</v>
       </c>
       <c r="DG66" s="0">
-        <v>-0.2522534364133987</v>
+        <v>-0.6755089885689185</v>
       </c>
       <c r="DH66" s="0">
-        <v>0.33305399877800995</v>
+        <v>-0.65465749800163209</v>
       </c>
       <c r="DI66" s="0">
-        <v>0.17821349506012302</v>
+        <v>-0.62531526311011365</v>
       </c>
     </row>
     <row r="67">
@@ -23427,40 +23427,40 @@
         <v>-0.30535916609036801</v>
       </c>
       <c r="CX67" s="0">
-        <v>0.14786362926152799</v>
+        <v>0.14786364135907001</v>
       </c>
       <c r="CY67" s="0">
-        <v>0.24819678000214701</v>
+        <v>0.75071767126201305</v>
       </c>
       <c r="CZ67" s="0">
-        <v>0.30713610098434801</v>
+        <v>0.30713607504537199</v>
       </c>
       <c r="DA67" s="0">
-        <v>0.33326673718990002</v>
+        <v>0.33329010534513698</v>
       </c>
       <c r="DB67" s="0">
-        <v>-0.088163987174583999</v>
+        <v>0.73940589086836195</v>
       </c>
       <c r="DC67" s="0">
-        <v>0.27125855879493699</v>
+        <v>0.27124314458131299</v>
       </c>
       <c r="DD67" s="0">
-        <v>0.095568120200171899</v>
+        <v>0.095570128980342603</v>
       </c>
       <c r="DE67" s="0">
-        <v>-0.051576798099369402</v>
+        <v>0.74536757109729501</v>
       </c>
       <c r="DF67" s="0">
-        <v>0.242923565176244</v>
+        <v>0.24292700155380001</v>
       </c>
       <c r="DG67" s="0">
-        <v>-0.10033315074061902</v>
+        <v>-0.60285402990294301</v>
       </c>
       <c r="DH67" s="0">
-        <v>0.42143072436448403</v>
+        <v>-0.40611578552322497</v>
       </c>
       <c r="DI67" s="0">
-        <v>0.14714491829954129</v>
+        <v>-0.64979744211695245</v>
       </c>
     </row>
     <row r="68">
@@ -23768,40 +23768,40 @@
         <v>0.82936459647126703</v>
       </c>
       <c r="CX68" s="0">
-        <v>6.0461477095596301e-10</v>
+        <v>1.68902988545506e-08</v>
       </c>
       <c r="CY68" s="0">
-        <v>0.24999986071010999</v>
+        <v>0.75000800956997704</v>
       </c>
       <c r="CZ68" s="0">
-        <v>26.4632907476594</v>
+        <v>18.951340271564199</v>
       </c>
       <c r="DA68" s="0">
-        <v>-24.965</v>
+        <v>5.3009520909755302e-08</v>
       </c>
       <c r="DB68" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000022653625098</v>
       </c>
       <c r="DC68" s="0">
-        <v>37.108333333333299</v>
+        <v>18.8626600355921</v>
       </c>
       <c r="DD68" s="0">
-        <v>-0.190979485866837</v>
+        <v>2.8994094455442102e-07</v>
       </c>
       <c r="DE68" s="0">
-        <v>-320.92922063252797</v>
+        <v>0.75001679683964595</v>
       </c>
       <c r="DF68" s="0">
-        <v>181.619269596511</v>
+        <v>17.243974122718701</v>
       </c>
       <c r="DG68" s="0">
-        <v>-0.24999986010549521</v>
+        <v>-0.75000799267967821</v>
       </c>
       <c r="DH68" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.7500001735267301</v>
       </c>
       <c r="DI68" s="0">
-        <v>320.73824114666115</v>
+        <v>-0.75001650689870136</v>
       </c>
     </row>
     <row r="69">
@@ -24109,40 +24109,40 @@
         <v>0.86330888817798102</v>
       </c>
       <c r="CX69" s="0">
-        <v>3.8367835463437603e-09</v>
+        <v>3.7082166940514001e-09</v>
       </c>
       <c r="CY69" s="0">
-        <v>0.37412324742490299</v>
+        <v>0.74999999889931401</v>
       </c>
       <c r="CZ69" s="0">
-        <v>19.026275622256499</v>
+        <v>19.612448591441201</v>
       </c>
       <c r="DA69" s="0">
-        <v>-24.965</v>
+        <v>5.2675524669924097e-08</v>
       </c>
       <c r="DB69" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.88976497952946498</v>
       </c>
       <c r="DC69" s="0">
-        <v>37.108333333333299</v>
+        <v>18.985754846056299</v>
       </c>
       <c r="DD69" s="0">
-        <v>-0.21000934093013501</v>
+        <v>5.3238145291653303e-08</v>
       </c>
       <c r="DE69" s="0">
-        <v>-254.176340703432</v>
+        <v>0.75013262695205096</v>
       </c>
       <c r="DF69" s="0">
-        <v>143.90520323029099</v>
+        <v>18.747268224749099</v>
       </c>
       <c r="DG69" s="0">
-        <v>-0.37412324358811944</v>
+        <v>-0.74999999519109728</v>
       </c>
       <c r="DH69" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.88976492685394026</v>
       </c>
       <c r="DI69" s="0">
-        <v>253.96633136250188</v>
+        <v>-0.75013257371390563</v>
       </c>
     </row>
     <row r="70">
@@ -24450,40 +24450,40 @@
         <v>0.66254053748989605</v>
       </c>
       <c r="CX70" s="0">
-        <v>4.4848321980658602e-09</v>
+        <v>4.4846143509401499e-09</v>
       </c>
       <c r="CY70" s="0">
-        <v>0.24331443331473601</v>
+        <v>0.75197649703505398</v>
       </c>
       <c r="CZ70" s="0">
-        <v>2.8259138232150902</v>
+        <v>2.8259148438104398</v>
       </c>
       <c r="DA70" s="0">
-        <v>-0.37974114403840498</v>
+        <v>7.70695814333961e-10</v>
       </c>
       <c r="DB70" s="0">
-        <v>-1.1859149845829</v>
+        <v>0.83731404708267798</v>
       </c>
       <c r="DC70" s="0">
-        <v>2.3354185492438102</v>
+        <v>2.8259148421825802</v>
       </c>
       <c r="DD70" s="0">
-        <v>-0.21185622914319199</v>
+        <v>1.4999319650156401e-08</v>
       </c>
       <c r="DE70" s="0">
-        <v>-2.7799407013883699</v>
+        <v>0.85575407192653097</v>
       </c>
       <c r="DF70" s="0">
-        <v>2.09891978961728</v>
+        <v>2.8259148603772801</v>
       </c>
       <c r="DG70" s="0">
-        <v>-0.24331442882990381</v>
+        <v>-0.75197649255043963</v>
       </c>
       <c r="DH70" s="0">
-        <v>0.80617384054449504</v>
+        <v>-0.83731404631198214</v>
       </c>
       <c r="DI70" s="0">
-        <v>2.5680844722451779</v>
+        <v>-0.85575405692721129</v>
       </c>
     </row>
     <row r="71">
@@ -24791,40 +24791,40 @@
         <v>0.19712820371273301</v>
       </c>
       <c r="CX71" s="0">
-        <v>0.112566436301533</v>
+        <v>0.112566441649935</v>
       </c>
       <c r="CY71" s="0">
-        <v>0.24891153546774999</v>
+        <v>0.75314430679787803</v>
       </c>
       <c r="CZ71" s="0">
-        <v>0.66808744544850296</v>
+        <v>0.668087477246602</v>
       </c>
       <c r="DA71" s="0">
-        <v>0.43196899067399802</v>
+        <v>0.43197035509225201</v>
       </c>
       <c r="DB71" s="0">
-        <v>-0.42204514869987703</v>
+        <v>0.68077716312487602</v>
       </c>
       <c r="DC71" s="0">
-        <v>0.75223543711265395</v>
+        <v>0.75224283657886004</v>
       </c>
       <c r="DD71" s="0">
-        <v>0.60241366133331797</v>
+        <v>0.60244859775450899</v>
       </c>
       <c r="DE71" s="0">
-        <v>-0.408379635945125</v>
+        <v>0.75835509386463296</v>
       </c>
       <c r="DF71" s="0">
-        <v>1.22941946733894</v>
+        <v>1.2294213800843301</v>
       </c>
       <c r="DG71" s="0">
-        <v>-0.13634509916621701</v>
+        <v>-0.64057786514794302</v>
       </c>
       <c r="DH71" s="0">
-        <v>0.85401413937387505</v>
+        <v>-0.24880680803262401</v>
       </c>
       <c r="DI71" s="0">
-        <v>1.010793297278443</v>
+        <v>-0.15590649611012397</v>
       </c>
     </row>
     <row r="72">
@@ -25132,40 +25132,40 @@
         <v>0.68033575719640904</v>
       </c>
       <c r="CX72" s="0">
-        <v>1.2357004165055101e-08</v>
+        <v>2.47142470353547e-09</v>
       </c>
       <c r="CY72" s="0">
-        <v>0.3414495152257</v>
+        <v>0.74557665379852101</v>
       </c>
       <c r="CZ72" s="0">
-        <v>2.1928295536877802</v>
+        <v>2.19282372990157</v>
       </c>
       <c r="DA72" s="0">
-        <v>-0.122561746241235</v>
+        <v>2.14403132773261e-07</v>
       </c>
       <c r="DB72" s="0">
-        <v>-0.97015889360941798</v>
+        <v>0.73716239825701702</v>
       </c>
       <c r="DC72" s="0">
-        <v>1.98675398213162</v>
+        <v>2.1928241393499999</v>
       </c>
       <c r="DD72" s="0">
-        <v>-0.028496729858802899</v>
+        <v>1.0745192476371501e-07</v>
       </c>
       <c r="DE72" s="0">
-        <v>-1.7498038173375801</v>
+        <v>0.72459063652140998</v>
       </c>
       <c r="DF72" s="0">
-        <v>2.0609972285820501</v>
+        <v>2.1928243573474999</v>
       </c>
       <c r="DG72" s="0">
-        <v>-0.34144950286869585</v>
+        <v>-0.74557665132709627</v>
       </c>
       <c r="DH72" s="0">
-        <v>0.84759714736818292</v>
+        <v>-0.73716218385388421</v>
       </c>
       <c r="DI72" s="0">
-        <v>1.7213070874787773</v>
+        <v>-0.72459052906948518</v>
       </c>
     </row>
     <row r="73">
@@ -25461,40 +25461,40 @@
         <v>0.83277622856017197</v>
       </c>
       <c r="CX73" s="0">
-        <v>1.7420516471170099e-10</v>
+        <v>2.6111329066797001e-09</v>
       </c>
       <c r="CY73" s="0">
-        <v>0.42927237477190999</v>
+        <v>0.75000000176239201</v>
       </c>
       <c r="CZ73" s="0">
-        <v>15.275236365121801</v>
+        <v>20.418666478382299</v>
       </c>
       <c r="DA73" s="0">
-        <v>-24.965</v>
+        <v>4.2626356337134103e-08</v>
       </c>
       <c r="DB73" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74995735764902105</v>
       </c>
       <c r="DC73" s="0">
-        <v>37.108333333333299</v>
+        <v>18.764849574378601</v>
       </c>
       <c r="DD73" s="0">
-        <v>-0.22674014629865999</v>
+        <v>3.60881168412449e-10</v>
       </c>
       <c r="DE73" s="0">
-        <v>-244.186805025718</v>
+        <v>0.73796013959490203</v>
       </c>
       <c r="DF73" s="0">
-        <v>138.30813677601</v>
+        <v>22.1676526046597</v>
       </c>
       <c r="DG73" s="0">
-        <v>-0.42927237459770484</v>
+        <v>-0.74999999915125914</v>
       </c>
       <c r="DH73" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74995731502266472</v>
       </c>
       <c r="DI73" s="0">
-        <v>243.96006487941935</v>
+        <v>-0.73796013923402082</v>
       </c>
     </row>
     <row r="74">
@@ -25802,40 +25802,40 @@
         <v>0.84066850534225501</v>
       </c>
       <c r="CX74" s="0">
-        <v>0.041121122021522398</v>
+        <v>0.041121120382952403</v>
       </c>
       <c r="CY74" s="0">
-        <v>0.24986225798426201</v>
+        <v>0.74093103848743402</v>
       </c>
       <c r="CZ74" s="0">
-        <v>2.09729260282811</v>
+        <v>2.09729257158827</v>
       </c>
       <c r="DA74" s="0">
-        <v>0.091361013660355206</v>
+        <v>0.091362073377366501</v>
       </c>
       <c r="DB74" s="0">
-        <v>1.0364459969348001</v>
+        <v>0.72898858074909501</v>
       </c>
       <c r="DC74" s="0">
-        <v>1.97630504146254</v>
+        <v>1.9762460876082999</v>
       </c>
       <c r="DD74" s="0">
-        <v>0.102013031867896</v>
+        <v>0.102013064545164</v>
       </c>
       <c r="DE74" s="0">
-        <v>-3.62529243657321</v>
+        <v>0.73455642277944899</v>
       </c>
       <c r="DF74" s="0">
-        <v>2.3021747016449199</v>
+        <v>2.3021555073481901</v>
       </c>
       <c r="DG74" s="0">
-        <v>-0.2087411359627396</v>
+        <v>-0.69980991810448168</v>
       </c>
       <c r="DH74" s="0">
-        <v>-0.9450849832744449</v>
+        <v>-0.63762650737172855</v>
       </c>
       <c r="DI74" s="0">
-        <v>3.7273054684411058</v>
+        <v>-0.63254335823428498</v>
       </c>
     </row>
     <row r="75">
@@ -26143,40 +26143,40 @@
         <v>0.49372141804720798</v>
       </c>
       <c r="CX75" s="0">
-        <v>0.079114275330828904</v>
+        <v>0.079114290785250202</v>
       </c>
       <c r="CY75" s="0">
-        <v>0.25007637881231698</v>
+        <v>0.75003635346445297</v>
       </c>
       <c r="CZ75" s="0">
-        <v>0.75954441696424901</v>
+        <v>0.75954447622502796</v>
       </c>
       <c r="DA75" s="0">
-        <v>0.27006271201954002</v>
+        <v>0.27004874687146002</v>
       </c>
       <c r="DB75" s="0">
-        <v>0.321616278466129</v>
+        <v>0.73639662237390602</v>
       </c>
       <c r="DC75" s="0">
-        <v>0.78320850535123998</v>
+        <v>0.78318990399649102</v>
       </c>
       <c r="DD75" s="0">
-        <v>0.51776467073680699</v>
+        <v>0.51775090623796605</v>
       </c>
       <c r="DE75" s="0">
-        <v>-0.44318935557264399</v>
+        <v>0.70671570731945199</v>
       </c>
       <c r="DF75" s="0">
-        <v>1.23900586309817</v>
+        <v>1.2390243228164699</v>
       </c>
       <c r="DG75" s="0">
-        <v>-0.17096210348148808</v>
+        <v>-0.67092206267920274</v>
       </c>
       <c r="DH75" s="0">
-        <v>-0.051553566446588983</v>
+        <v>-0.466347875502446</v>
       </c>
       <c r="DI75" s="0">
-        <v>0.96095402630945093</v>
+        <v>-0.18896480108148594</v>
       </c>
     </row>
     <row r="76">
@@ -26484,40 +26484,40 @@
         <v>0.522331716849048</v>
       </c>
       <c r="CX76" s="0">
-        <v>0.048843413549060299</v>
+        <v>0.0488434122840814</v>
       </c>
       <c r="CY76" s="0">
-        <v>0.25005897279285</v>
+        <v>0.75009766579192405</v>
       </c>
       <c r="CZ76" s="0">
-        <v>0.95101928262648605</v>
+        <v>0.95101929657104001</v>
       </c>
       <c r="DA76" s="0">
-        <v>0.050123323199618298</v>
+        <v>0.0501228667397512</v>
       </c>
       <c r="DB76" s="0">
-        <v>-1.75561751624482</v>
+        <v>0.65256406750185503</v>
       </c>
       <c r="DC76" s="0">
-        <v>0.86298451702942403</v>
+        <v>0.86298887791582501</v>
       </c>
       <c r="DD76" s="0">
-        <v>0.090691266624100694</v>
+        <v>0.090687004075398106</v>
       </c>
       <c r="DE76" s="0">
-        <v>-0.73382741042729105</v>
+        <v>0.74998582078658704</v>
       </c>
       <c r="DF76" s="0">
-        <v>1.0001171821518</v>
+        <v>1.0001356877709699</v>
       </c>
       <c r="DG76" s="0">
-        <v>-0.2012155592437897</v>
+        <v>-0.70125425350784265</v>
       </c>
       <c r="DH76" s="0">
-        <v>1.8057408394444383</v>
+        <v>-0.60244120076210383</v>
       </c>
       <c r="DI76" s="0">
-        <v>0.8245186770513917</v>
+        <v>-0.65929881671118895</v>
       </c>
     </row>
     <row r="77">
@@ -26825,40 +26825,40 @@
         <v>0.83538016507034996</v>
       </c>
       <c r="CX77" s="0">
-        <v>3.6825723115280898e-09</v>
+        <v>1.76066341392884e-08</v>
       </c>
       <c r="CY77" s="0">
-        <v>0.230600815950632</v>
+        <v>0.749992559131614</v>
       </c>
       <c r="CZ77" s="0">
-        <v>23.2324646315402</v>
+        <v>19.1309797168975</v>
       </c>
       <c r="DA77" s="0">
-        <v>-0.013377363387858301</v>
+        <v>8.4557760152526399e-08</v>
       </c>
       <c r="DB77" s="0">
-        <v>-0.82142737154350798</v>
+        <v>0.74999633853389502</v>
       </c>
       <c r="DC77" s="0">
-        <v>28.234590718633498</v>
+        <v>18.921516233651001</v>
       </c>
       <c r="DD77" s="0">
-        <v>-0.0466295947907178</v>
+        <v>8.8905718136376101e-08</v>
       </c>
       <c r="DE77" s="0">
-        <v>-12.4491206721616</v>
+        <v>1.13042109315449</v>
       </c>
       <c r="DF77" s="0">
-        <v>7.32637935535924</v>
+        <v>17.9919223308321</v>
       </c>
       <c r="DG77" s="0">
-        <v>-0.2306008122680597</v>
+        <v>-0.74999254152497985</v>
       </c>
       <c r="DH77" s="0">
-        <v>0.80805000815564965</v>
+        <v>-0.7499962539761349</v>
       </c>
       <c r="DI77" s="0">
-        <v>12.402491077370883</v>
+        <v>-1.1304210042487719</v>
       </c>
     </row>
     <row r="78">
@@ -27166,40 +27166,40 @@
         <v>1.1952862964866799</v>
       </c>
       <c r="CX78" s="0">
-        <v>0.072076798315565002</v>
+        <v>0.072076796624604395</v>
       </c>
       <c r="CY78" s="0">
-        <v>0.25064692338658501</v>
+        <v>0.74963588274031701</v>
       </c>
       <c r="CZ78" s="0">
-        <v>2.9029287671447301</v>
+        <v>2.9029288589363098</v>
       </c>
       <c r="DA78" s="0">
-        <v>0.26322223088136498</v>
+        <v>0.26322091105534301</v>
       </c>
       <c r="DB78" s="0">
-        <v>-1.3635226544501899</v>
+        <v>0.76540038875472605</v>
       </c>
       <c r="DC78" s="0">
-        <v>3.1517035415514498</v>
+        <v>3.1516665618997899</v>
       </c>
       <c r="DD78" s="0">
-        <v>0.25631077694135701</v>
+        <v>0.25631105742316002</v>
       </c>
       <c r="DE78" s="0">
-        <v>-7.1439574808414203</v>
+        <v>0.75549196893998105</v>
       </c>
       <c r="DF78" s="0">
-        <v>4.2635417223329304</v>
+        <v>4.2635359286253598</v>
       </c>
       <c r="DG78" s="0">
-        <v>-0.17857012507101999</v>
+        <v>-0.67755908611571258</v>
       </c>
       <c r="DH78" s="0">
-        <v>1.6267448853315549</v>
+        <v>-0.50217947769938309</v>
       </c>
       <c r="DI78" s="0">
-        <v>7.400268257782777</v>
+        <v>-0.49918091151682104</v>
       </c>
     </row>
     <row r="79">
@@ -27507,40 +27507,40 @@
         <v>0.87092074870949998</v>
       </c>
       <c r="CX79" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY79" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ79" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA79" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB79" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC79" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD79" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE79" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF79" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG79" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH79" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI79" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="80">
@@ -27848,40 +27848,40 @@
         <v>0.87092074870949998</v>
       </c>
       <c r="CX80" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY80" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ80" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA80" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB80" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC80" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD80" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE80" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF80" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG80" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH80" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI80" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="81">
@@ -28189,40 +28189,40 @@
         <v>0.82831539346090699</v>
       </c>
       <c r="CX81" s="0">
-        <v>3.0634205647939703e-08</v>
+        <v>1.67053322690279e-07</v>
       </c>
       <c r="CY81" s="0">
-        <v>0.25014550133858598</v>
+        <v>0.74996327531205997</v>
       </c>
       <c r="CZ81" s="0">
-        <v>18.6230209543351</v>
+        <v>17.104507303082102</v>
       </c>
       <c r="DA81" s="0">
-        <v>-24.965</v>
+        <v>7.1346819787909004e-08</v>
       </c>
       <c r="DB81" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74999514187309202</v>
       </c>
       <c r="DC81" s="0">
-        <v>37.108333333333299</v>
+        <v>18.688602894952901</v>
       </c>
       <c r="DD81" s="0">
-        <v>-0.21275301638899</v>
+        <v>1.33386398955855e-08</v>
       </c>
       <c r="DE81" s="0">
-        <v>-256.34614975713401</v>
+        <v>0.74841924226319401</v>
       </c>
       <c r="DF81" s="0">
-        <v>145.13176548878499</v>
+        <v>20.022387122199099</v>
       </c>
       <c r="DG81" s="0">
-        <v>-0.25014547070438031</v>
+        <v>-0.74996310825873724</v>
       </c>
       <c r="DH81" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74999507052627223</v>
       </c>
       <c r="DI81" s="0">
-        <v>256.13339674074501</v>
+        <v>-0.74841922892455415</v>
       </c>
     </row>
     <row r="82">
@@ -28530,40 +28530,40 @@
         <v>0.83533951395125905</v>
       </c>
       <c r="CX82" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="CY82" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="CZ82" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="DA82" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="DB82" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="DC82" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="DD82" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="DE82" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="DF82" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="DG82" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="DH82" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="DI82" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
     </row>
     <row r="83">
@@ -28871,40 +28871,40 @@
         <v>0.041427831441735903</v>
       </c>
       <c r="CX83" s="0">
-        <v>7.3168852761458003e-09</v>
+        <v>7.31688419373936e-09</v>
       </c>
       <c r="CY83" s="0">
-        <v>0.24853314435763399</v>
+        <v>0.69959804519805102</v>
       </c>
       <c r="CZ83" s="0">
-        <v>1.5700161791673299</v>
+        <v>1.5700160793495701</v>
       </c>
       <c r="DA83" s="0">
-        <v>-35.6470244857571</v>
+        <v>5.2983012828679097e-07</v>
       </c>
       <c r="DB83" s="0">
-        <v>20.949980456985902</v>
+        <v>0.57257427264872596</v>
       </c>
       <c r="DC83" s="0">
-        <v>0.96107756322725302</v>
+        <v>1.5700183633287801</v>
       </c>
       <c r="DD83" s="0">
-        <v>-0.24999999962132199</v>
+        <v>3.6652468480504899e-07</v>
       </c>
       <c r="DE83" s="0">
-        <v>-1.2993688863498001</v>
+        <v>0.61084978455068495</v>
       </c>
       <c r="DF83" s="0">
-        <v>1.3172509011337401</v>
+        <v>1.57001719991897</v>
       </c>
       <c r="DG83" s="0">
-        <v>-0.24853313704074873</v>
+        <v>-0.69959803788116681</v>
       </c>
       <c r="DH83" s="0">
-        <v>-56.597004942742998</v>
+        <v>-0.57257374281859763</v>
       </c>
       <c r="DI83" s="0">
-        <v>1.0493688867284781</v>
+        <v>-0.61084941802600012</v>
       </c>
     </row>
     <row r="84">
@@ -29212,40 +29212,40 @@
         <v>1.0325034178700701</v>
       </c>
       <c r="CX84" s="0">
-        <v>9.2487830551900599e-07</v>
+        <v>9.2505284807292707e-09</v>
       </c>
       <c r="CY84" s="0">
-        <v>0.25323640981177298</v>
+        <v>0.74000943191457502</v>
       </c>
       <c r="CZ84" s="0">
-        <v>2.1470511890785202</v>
+        <v>2.14704664093769</v>
       </c>
       <c r="DA84" s="0">
-        <v>-0.31925920750638398</v>
+        <v>1.15749774282915e-07</v>
       </c>
       <c r="DB84" s="0">
-        <v>-0.73130614840855701</v>
+        <v>0.73812908328460103</v>
       </c>
       <c r="DC84" s="0">
-        <v>1.8064802357844501</v>
+        <v>2.1470459634536501</v>
       </c>
       <c r="DD84" s="0">
-        <v>-0.0248183885224595</v>
+        <v>8.0971019946432006e-08</v>
       </c>
       <c r="DE84" s="0">
-        <v>-2.0190323774943399</v>
+        <v>0.72643678593100303</v>
       </c>
       <c r="DF84" s="0">
-        <v>2.0463631747986599</v>
+        <v>2.1470459330610199</v>
       </c>
       <c r="DG84" s="0">
-        <v>-0.25323548493346748</v>
+        <v>-0.74000942266404657</v>
       </c>
       <c r="DH84" s="0">
-        <v>0.41204694090217303</v>
+        <v>-0.73812896753482671</v>
       </c>
       <c r="DI84" s="0">
-        <v>1.9942139889718804</v>
+        <v>-0.72643670495998303</v>
       </c>
     </row>
     <row r="85">
@@ -29553,40 +29553,40 @@
         <v>0.53366778250101599</v>
       </c>
       <c r="CX85" s="0">
-        <v>0.044189793107494303</v>
+        <v>0.044189798171648802</v>
       </c>
       <c r="CY85" s="0">
-        <v>0.25004536522222198</v>
+        <v>0.75142137302591505</v>
       </c>
       <c r="CZ85" s="0">
-        <v>1.0108910004065399</v>
+        <v>1.0108909903136101</v>
       </c>
       <c r="DA85" s="0">
-        <v>0.0132840388140174</v>
+        <v>0.0132816886795267</v>
       </c>
       <c r="DB85" s="0">
-        <v>-0.78353066500979895</v>
+        <v>0.75610836474561804</v>
       </c>
       <c r="DC85" s="0">
-        <v>0.898466347582487</v>
+        <v>0.89847627919784301</v>
       </c>
       <c r="DD85" s="0">
-        <v>0.13304204596365299</v>
+        <v>0.13304415181500401</v>
       </c>
       <c r="DE85" s="0">
-        <v>-0.81718174631026297</v>
+        <v>0.74224280770288498</v>
       </c>
       <c r="DF85" s="0">
-        <v>1.18421398653238</v>
+        <v>1.1841868248051</v>
       </c>
       <c r="DG85" s="0">
-        <v>-0.20585557211472769</v>
+        <v>-0.70723157485426624</v>
       </c>
       <c r="DH85" s="0">
-        <v>0.79681470382381636</v>
+        <v>-0.74282667606609132</v>
       </c>
       <c r="DI85" s="0">
-        <v>0.95022379227391596</v>
+        <v>-0.60919865588788102</v>
       </c>
     </row>
   </sheetData>
